--- a/research/traditional_assets/database/data/thailand/thailand_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_telecom_equipment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="set_dtcent" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,43 +590,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0823</v>
+        <v>-0.063</v>
       </c>
       <c r="G2">
-        <v>-0.06051948051948052</v>
+        <v>0.06148796498905907</v>
       </c>
       <c r="H2">
-        <v>-0.06051948051948052</v>
+        <v>0.06148796498905907</v>
       </c>
       <c r="I2">
-        <v>-0.06311688311688313</v>
+        <v>0.02407002188183807</v>
       </c>
       <c r="J2">
-        <v>-0.06311688311688313</v>
+        <v>0.02125553507124519</v>
       </c>
       <c r="K2">
-        <v>-2.78</v>
+        <v>0.74</v>
       </c>
       <c r="L2">
-        <v>-0.07220779220779221</v>
+        <v>0.01619256017505471</v>
       </c>
       <c r="M2">
-        <v>3.03</v>
+        <v>4.24</v>
       </c>
       <c r="N2">
-        <v>0.03717791411042944</v>
+        <v>0.02828552368245497</v>
       </c>
       <c r="O2">
-        <v>-1.089928057553957</v>
+        <v>5.72972972972973</v>
       </c>
       <c r="P2">
-        <v>3.03</v>
+        <v>4.24</v>
       </c>
       <c r="Q2">
-        <v>0.03717791411042944</v>
+        <v>0.02828552368245497</v>
       </c>
       <c r="R2">
-        <v>-1.089928057553957</v>
+        <v>5.72972972972973</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +635,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>15.8</v>
+        <v>17.57</v>
       </c>
       <c r="V2">
-        <v>0.1938650306748466</v>
-      </c>
-      <c r="W2">
-        <v>-0.05419103313840156</v>
+        <v>0.1172114743162108</v>
       </c>
       <c r="X2">
-        <v>0.09071873835334049</v>
-      </c>
-      <c r="Y2">
-        <v>-0.1449097714917421</v>
+        <v>0.1484983988056744</v>
       </c>
       <c r="Z2">
-        <v>0.5378597373568036</v>
-      </c>
-      <c r="AA2">
-        <v>-0.03394803017602683</v>
+        <v>0.8606403013182673</v>
       </c>
       <c r="AB2">
-        <v>0.08109011554776294</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1150381457237898</v>
+        <v>0.1405969013031872</v>
       </c>
       <c r="AD2">
-        <v>16.4</v>
+        <v>14.02</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>16.4</v>
+        <v>14.02</v>
       </c>
       <c r="AG2">
-        <v>0.5999999999999979</v>
+        <v>-3.550000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1675178753830439</v>
+        <v>0.08552952659834065</v>
       </c>
       <c r="AI2">
-        <v>0.2380261248185776</v>
+        <v>0.1876338329764454</v>
       </c>
       <c r="AJ2">
-        <v>0.007308160779537124</v>
+        <v>-0.0242569183464298</v>
       </c>
       <c r="AK2">
-        <v>0.01129943502824855</v>
+        <v>-0.06211723534558181</v>
       </c>
       <c r="AL2">
-        <v>0.482</v>
+        <v>0.5389999999999999</v>
       </c>
       <c r="AM2">
-        <v>0.15</v>
+        <v>0.2199999999999999</v>
       </c>
       <c r="AN2">
-        <v>-107.8947368421053</v>
+        <v>2.954066582385166</v>
       </c>
       <c r="AO2">
-        <v>-5.041493775933611</v>
+        <v>2.040816326530612</v>
       </c>
       <c r="AP2">
-        <v>-3.947368421052618</v>
+        <v>-0.7479983143699959</v>
       </c>
       <c r="AQ2">
-        <v>-16.20000000000001</v>
+        <v>5.000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -710,127 +700,8949 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>D.T.C. Enterprise Public Company Limited (SET:DTCENT)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Telecom. Equipment</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0.2796407185628743</v>
+      </c>
+      <c r="H3">
+        <v>0.2796407185628743</v>
+      </c>
+      <c r="I3">
+        <v>0.1502994011976048</v>
+      </c>
+      <c r="J3">
+        <v>0.1151506435947004</v>
+      </c>
+      <c r="K3">
+        <v>1.96</v>
+      </c>
+      <c r="L3">
+        <v>0.1173652694610779</v>
+      </c>
+      <c r="M3">
+        <v>4.24</v>
+      </c>
+      <c r="N3">
+        <v>0.05737483085250338</v>
+      </c>
+      <c r="O3">
+        <v>2.163265306122449</v>
+      </c>
+      <c r="P3">
+        <v>4.24</v>
+      </c>
+      <c r="Q3">
+        <v>0.05737483085250338</v>
+      </c>
+      <c r="R3">
+        <v>2.163265306122449</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>6.97</v>
+      </c>
+      <c r="V3">
+        <v>0.09431664411366711</v>
+      </c>
+      <c r="X3">
+        <v>0.1434919835290071</v>
+      </c>
+      <c r="AB3">
+        <v>0.1410324016818173</v>
+      </c>
+      <c r="AD3">
+        <v>2.32</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>2.32</v>
+      </c>
+      <c r="AG3">
+        <v>-4.65</v>
+      </c>
+      <c r="AH3">
+        <v>0.03043820519548675</v>
+      </c>
+      <c r="AI3">
+        <v>0.1324200913242009</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.06714801444043322</v>
+      </c>
+      <c r="AK3">
+        <v>-0.4407582938388626</v>
+      </c>
+      <c r="AL3">
+        <v>0.129</v>
+      </c>
+      <c r="AM3">
+        <v>0.129</v>
+      </c>
+      <c r="AN3">
+        <v>0.5903307888040712</v>
+      </c>
+      <c r="AO3">
+        <v>19.45736434108527</v>
+      </c>
+      <c r="AP3">
+        <v>-1.183206106870229</v>
+      </c>
+      <c r="AQ3">
+        <v>19.45736434108527</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>ALT Telecom Public Company Limited (SET:ALT)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Telecom. Equipment</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.063</v>
+      </c>
+      <c r="G4">
+        <v>-0.06413793103448276</v>
+      </c>
+      <c r="H4">
+        <v>-0.06413793103448276</v>
+      </c>
+      <c r="I4">
+        <v>-0.04862068965517241</v>
+      </c>
+      <c r="J4">
+        <v>-0.04862068965517241</v>
+      </c>
+      <c r="K4">
+        <v>-1.22</v>
+      </c>
+      <c r="L4">
+        <v>-0.04206896551724138</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>10.6</v>
+      </c>
+      <c r="V4">
+        <v>0.1394736842105263</v>
+      </c>
+      <c r="W4">
+        <v>-0.02323809523809524</v>
+      </c>
+      <c r="X4">
+        <v>0.1535048140823418</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1767429093204371</v>
+      </c>
+      <c r="Z4">
+        <v>0.5461393596986817</v>
+      </c>
+      <c r="AA4">
+        <v>-0.02655367231638418</v>
+      </c>
+      <c r="AB4">
+        <v>0.1401614009245572</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1667150732409414</v>
+      </c>
+      <c r="AD4">
+        <v>11.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>11.7</v>
+      </c>
+      <c r="AG4">
+        <v>1.1</v>
+      </c>
+      <c r="AH4">
+        <v>0.1334093500570125</v>
+      </c>
+      <c r="AI4">
+        <v>0.2045454545454545</v>
+      </c>
+      <c r="AJ4">
+        <v>0.01426718547341115</v>
+      </c>
+      <c r="AK4">
+        <v>0.02360515021459227</v>
+      </c>
+      <c r="AL4">
+        <v>0.41</v>
+      </c>
+      <c r="AM4">
+        <v>0.09099999999999997</v>
+      </c>
+      <c r="AN4">
+        <v>14.33823529411765</v>
+      </c>
+      <c r="AO4">
+        <v>-3.439024390243902</v>
+      </c>
+      <c r="AP4">
+        <v>1.348039215686274</v>
+      </c>
+      <c r="AQ4">
+        <v>-15.4945054945055</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D.T.C. Enterprise Public Company Limited (SET:DTCENT)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SET:DTCENT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Telecom. Equipment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0304382051954867</v>
+      </c>
+      <c r="F2">
+        <v>0.13</v>
+      </c>
+      <c r="G2">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="H2">
+        <v>67.7528867093513</v>
+      </c>
+      <c r="I2">
+        <v>69.25</v>
+      </c>
+      <c r="J2">
+        <v>70.6914867093513</v>
+      </c>
+      <c r="K2">
+        <v>2.32</v>
+      </c>
+      <c r="L2">
+        <v>9.9086</v>
+      </c>
+      <c r="M2">
+        <v>0.141032401681817</v>
+      </c>
+      <c r="N2">
+        <v>0.138947756767002</v>
+      </c>
+      <c r="O2">
+        <v>0.0626862385321101</v>
+      </c>
+      <c r="P2">
+        <v>0.044</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.143491983529007</v>
+      </c>
+      <c r="T2">
+        <v>0.153135352605749</v>
+      </c>
+      <c r="U2">
+        <v>1.20708680345606</v>
+      </c>
+      <c r="V2">
+        <v>1.31827376506489</v>
+      </c>
+      <c r="W2">
+        <v>4.605732761072566</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.08673111430699013</v>
+      </c>
+      <c r="AC2">
+        <v>0.07835779816513762</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>3.93</v>
+      </c>
+      <c r="AH2">
+        <v>1.42</v>
+      </c>
+      <c r="AI2">
+        <v>1.845000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>2.32</v>
+      </c>
+      <c r="AK2">
+        <v>2.32</v>
+      </c>
+      <c r="AL2">
+        <v>0.129</v>
+      </c>
+      <c r="AM2">
+        <v>2.32</v>
+      </c>
+      <c r="AN2">
+        <v>6.97</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1409270603357308</v>
+      </c>
+      <c r="C2">
+        <v>76.29142953290257</v>
+      </c>
+      <c r="D2">
+        <v>69.32142953290257</v>
+      </c>
+      <c r="E2">
+        <v>-2.32</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>6.97</v>
+      </c>
+      <c r="H2">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.93</v>
+      </c>
+      <c r="K2">
+        <v>1.42</v>
+      </c>
+      <c r="L2">
+        <v>2.51</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2.51</v>
+      </c>
+      <c r="O2">
+        <v>0.5019999999999999</v>
+      </c>
+      <c r="P2">
+        <v>2.008</v>
+      </c>
+      <c r="Q2">
+        <v>3.428</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1409270603357308</v>
+      </c>
+      <c r="T2">
+        <v>1.177513527316688</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1407004062150593</v>
+      </c>
+      <c r="C3">
+        <v>75.68341917981436</v>
+      </c>
       <c r="D3">
-        <v>-0.0823</v>
+        <v>69.47561917981437</v>
+      </c>
+      <c r="E3">
+        <v>-1.5578</v>
+      </c>
+      <c r="F3">
+        <v>0.7622</v>
       </c>
       <c r="G3">
-        <v>-0.06051948051948052</v>
+        <v>6.97</v>
       </c>
       <c r="H3">
-        <v>-0.06051948051948052</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I3">
-        <v>-0.06311688311688313</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.06311688311688313</v>
+        <v>3.93</v>
       </c>
       <c r="K3">
-        <v>-2.78</v>
+        <v>1.42</v>
       </c>
       <c r="L3">
-        <v>-0.07220779220779221</v>
+        <v>2.51</v>
       </c>
       <c r="M3">
-        <v>3.03</v>
+        <v>0.03483254</v>
       </c>
       <c r="N3">
-        <v>0.03717791411042944</v>
+        <v>2.47516746</v>
       </c>
       <c r="O3">
-        <v>-1.089928057553957</v>
+        <v>0.4950334919999999</v>
       </c>
       <c r="P3">
-        <v>3.03</v>
+        <v>1.980133968</v>
       </c>
       <c r="Q3">
-        <v>0.03717791411042944</v>
+        <v>3.400133968</v>
       </c>
       <c r="R3">
-        <v>-1.089928057553957</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.1417523295101609</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.187028788143489</v>
       </c>
       <c r="U3">
-        <v>15.8</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.1938650306748466</v>
+        <v>0.2</v>
       </c>
       <c r="W3">
-        <v>-0.05419103313840156</v>
-      </c>
-      <c r="X3">
-        <v>0.09071873835334049</v>
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.1449097714917421</v>
+        <v>72.05905742159486</v>
       </c>
       <c r="Z3">
-        <v>0.5378597373568036</v>
-      </c>
-      <c r="AA3">
-        <v>-0.03394803017602683</v>
-      </c>
-      <c r="AB3">
-        <v>0.08109011554776294</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1150381457237898</v>
-      </c>
-      <c r="AD3">
-        <v>16.4</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>16.4</v>
-      </c>
-      <c r="AG3">
-        <v>0.5999999999999979</v>
-      </c>
-      <c r="AH3">
-        <v>0.1675178753830439</v>
-      </c>
-      <c r="AI3">
-        <v>0.2380261248185776</v>
-      </c>
-      <c r="AJ3">
-        <v>0.007308160779537124</v>
-      </c>
-      <c r="AK3">
-        <v>0.01129943502824855</v>
-      </c>
-      <c r="AL3">
-        <v>0.482</v>
-      </c>
-      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1404737520943878</v>
+      </c>
+      <c r="C4">
+        <v>75.0760962749243</v>
+      </c>
+      <c r="D4">
+        <v>69.6304962749243</v>
+      </c>
+      <c r="E4">
+        <v>-0.7955999999999999</v>
+      </c>
+      <c r="F4">
+        <v>1.5244</v>
+      </c>
+      <c r="G4">
+        <v>6.97</v>
+      </c>
+      <c r="H4">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3.93</v>
+      </c>
+      <c r="K4">
+        <v>1.42</v>
+      </c>
+      <c r="L4">
+        <v>2.51</v>
+      </c>
+      <c r="M4">
+        <v>0.06966508</v>
+      </c>
+      <c r="N4">
+        <v>2.44033492</v>
+      </c>
+      <c r="O4">
+        <v>0.4880669839999998</v>
+      </c>
+      <c r="P4">
+        <v>1.952267936</v>
+      </c>
+      <c r="Q4">
+        <v>3.372267936</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1425944409126407</v>
+      </c>
+      <c r="T4">
+        <v>1.196738237966756</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>36.02952871079743</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1402470979737164</v>
+      </c>
+      <c r="C5">
+        <v>74.4694654259433</v>
+      </c>
+      <c r="D5">
+        <v>69.78606542594329</v>
+      </c>
+      <c r="E5">
+        <v>-0.03339999999999987</v>
+      </c>
+      <c r="F5">
+        <v>2.2866</v>
+      </c>
+      <c r="G5">
+        <v>6.97</v>
+      </c>
+      <c r="H5">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.93</v>
+      </c>
+      <c r="K5">
+        <v>1.42</v>
+      </c>
+      <c r="L5">
+        <v>2.51</v>
+      </c>
+      <c r="M5">
+        <v>0.10449762</v>
+      </c>
+      <c r="N5">
+        <v>2.40550238</v>
+      </c>
+      <c r="O5">
+        <v>0.4811004759999998</v>
+      </c>
+      <c r="P5">
+        <v>1.924401904</v>
+      </c>
+      <c r="Q5">
+        <v>3.344401904</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.143453915436821</v>
+      </c>
+      <c r="T5">
+        <v>1.20664788263174</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>24.01968580719828</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1400204438530449</v>
+      </c>
+      <c r="C6">
+        <v>73.8635312818528</v>
+      </c>
+      <c r="D6">
+        <v>69.9423312818528</v>
+      </c>
+      <c r="E6">
+        <v>0.7288000000000001</v>
+      </c>
+      <c r="F6">
+        <v>3.0488</v>
+      </c>
+      <c r="G6">
+        <v>6.97</v>
+      </c>
+      <c r="H6">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.93</v>
+      </c>
+      <c r="K6">
+        <v>1.42</v>
+      </c>
+      <c r="L6">
+        <v>2.51</v>
+      </c>
+      <c r="M6">
+        <v>0.13933016</v>
+      </c>
+      <c r="N6">
+        <v>2.37066984</v>
+      </c>
+      <c r="O6">
+        <v>0.4741339679999999</v>
+      </c>
+      <c r="P6">
+        <v>1.896535872</v>
+      </c>
+      <c r="Q6">
+        <v>3.316535872</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1443312956802552</v>
+      </c>
+      <c r="T6">
+        <v>1.216763978227244</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03656</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>18.01476435539871</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1397937897323735</v>
+      </c>
+      <c r="C7">
+        <v>73.25829853336805</v>
+      </c>
+      <c r="D7">
+        <v>70.09929853336806</v>
+      </c>
+      <c r="E7">
+        <v>1.491</v>
+      </c>
+      <c r="F7">
+        <v>3.811</v>
+      </c>
+      <c r="G7">
+        <v>6.97</v>
+      </c>
+      <c r="H7">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.93</v>
+      </c>
+      <c r="K7">
+        <v>1.42</v>
+      </c>
+      <c r="L7">
+        <v>2.51</v>
+      </c>
+      <c r="M7">
+        <v>0.1741627</v>
+      </c>
+      <c r="N7">
+        <v>2.3358373</v>
+      </c>
+      <c r="O7">
+        <v>0.4671674599999998</v>
+      </c>
+      <c r="P7">
+        <v>1.86866984</v>
+      </c>
+      <c r="Q7">
+        <v>3.28866984</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1452271470867089</v>
+      </c>
+      <c r="T7">
+        <v>1.227093044256337</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03656</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>14.41181148431897</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.139643935611702</v>
+      </c>
+      <c r="C8">
+        <v>72.6002661134777</v>
+      </c>
+      <c r="D8">
+        <v>70.2034661134777</v>
+      </c>
+      <c r="E8">
+        <v>2.2532</v>
+      </c>
+      <c r="F8">
+        <v>4.5732</v>
+      </c>
+      <c r="G8">
+        <v>6.97</v>
+      </c>
+      <c r="H8">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.93</v>
+      </c>
+      <c r="K8">
+        <v>1.42</v>
+      </c>
+      <c r="L8">
+        <v>2.51</v>
+      </c>
+      <c r="M8">
+        <v>0.21631236</v>
+      </c>
+      <c r="N8">
+        <v>2.29368764</v>
+      </c>
+      <c r="O8">
+        <v>0.4587375279999999</v>
+      </c>
+      <c r="P8">
+        <v>1.834950112</v>
+      </c>
+      <c r="Q8">
+        <v>3.254950112</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1461420591613851</v>
+      </c>
+      <c r="T8">
+        <v>1.237641877647753</v>
+      </c>
+      <c r="U8">
+        <v>0.0473</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>11.60359028952391</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1396428814910305</v>
+      </c>
+      <c r="C9">
+        <v>71.83879995729239</v>
+      </c>
+      <c r="D9">
+        <v>70.2041999572924</v>
+      </c>
+      <c r="E9">
+        <v>3.015400000000001</v>
+      </c>
+      <c r="F9">
+        <v>5.335400000000001</v>
+      </c>
+      <c r="G9">
+        <v>6.97</v>
+      </c>
+      <c r="H9">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.93</v>
+      </c>
+      <c r="K9">
+        <v>1.42</v>
+      </c>
+      <c r="L9">
+        <v>2.51</v>
+      </c>
+      <c r="M9">
+        <v>0.2726389400000001</v>
+      </c>
+      <c r="N9">
+        <v>2.23736106</v>
+      </c>
+      <c r="O9">
+        <v>0.4474722119999998</v>
+      </c>
+      <c r="P9">
+        <v>1.789888848</v>
+      </c>
+      <c r="Q9">
+        <v>3.209888848</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.147076646764549</v>
+      </c>
+      <c r="T9">
+        <v>1.248417567671241</v>
+      </c>
+      <c r="U9">
+        <v>0.0511</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.04088</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>9.20631513605503</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1394594273703591</v>
+      </c>
+      <c r="C10">
+        <v>71.2045487257989</v>
+      </c>
+      <c r="D10">
+        <v>70.3321487257989</v>
+      </c>
+      <c r="E10">
+        <v>3.7776</v>
+      </c>
+      <c r="F10">
+        <v>6.0976</v>
+      </c>
+      <c r="G10">
+        <v>6.97</v>
+      </c>
+      <c r="H10">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.93</v>
+      </c>
+      <c r="K10">
+        <v>1.42</v>
+      </c>
+      <c r="L10">
+        <v>2.51</v>
+      </c>
+      <c r="M10">
+        <v>0.31158736</v>
+      </c>
+      <c r="N10">
+        <v>2.19841264</v>
+      </c>
+      <c r="O10">
+        <v>0.4396825279999999</v>
+      </c>
+      <c r="P10">
+        <v>1.758730112</v>
+      </c>
+      <c r="Q10">
+        <v>3.178730112</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1480315514895207</v>
+      </c>
+      <c r="T10">
+        <v>1.259427511825675</v>
+      </c>
+      <c r="U10">
+        <v>0.0511</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.04088</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>8.055525744048154</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1394127732496876</v>
+      </c>
+      <c r="C11">
+        <v>70.4749617275854</v>
+      </c>
+      <c r="D11">
+        <v>70.3647617275854</v>
+      </c>
+      <c r="E11">
+        <v>4.5398</v>
+      </c>
+      <c r="F11">
+        <v>6.8598</v>
+      </c>
+      <c r="G11">
+        <v>6.97</v>
+      </c>
+      <c r="H11">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.93</v>
+      </c>
+      <c r="K11">
+        <v>1.42</v>
+      </c>
+      <c r="L11">
+        <v>2.51</v>
+      </c>
+      <c r="M11">
+        <v>0.3635694</v>
+      </c>
+      <c r="N11">
+        <v>2.1464306</v>
+      </c>
+      <c r="O11">
+        <v>0.4292861199999998</v>
+      </c>
+      <c r="P11">
+        <v>1.71714448</v>
+      </c>
+      <c r="Q11">
+        <v>3.13714448</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1490074431315249</v>
+      </c>
+      <c r="T11">
+        <v>1.270679432774711</v>
+      </c>
+      <c r="U11">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>6.903771329490324</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1394045191290162</v>
+      </c>
+      <c r="C12">
+        <v>69.71853482047774</v>
+      </c>
+      <c r="D12">
+        <v>70.37053482047774</v>
+      </c>
+      <c r="E12">
+        <v>5.302</v>
+      </c>
+      <c r="F12">
+        <v>7.622</v>
+      </c>
+      <c r="G12">
+        <v>6.97</v>
+      </c>
+      <c r="H12">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.93</v>
+      </c>
+      <c r="K12">
+        <v>1.42</v>
+      </c>
+      <c r="L12">
+        <v>2.51</v>
+      </c>
+      <c r="M12">
+        <v>0.41921</v>
+      </c>
+      <c r="N12">
+        <v>2.09079</v>
+      </c>
+      <c r="O12">
+        <v>0.4181579999999999</v>
+      </c>
+      <c r="P12">
+        <v>1.672632</v>
+      </c>
+      <c r="Q12">
+        <v>3.092632</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1500050212544624</v>
+      </c>
+      <c r="T12">
+        <v>1.282181396411505</v>
+      </c>
+      <c r="U12">
+        <v>0.055</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.044</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>5.987452589394336</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1392522650083447</v>
+      </c>
+      <c r="C13">
+        <v>69.06299447518418</v>
+      </c>
+      <c r="D13">
+        <v>70.47719447518418</v>
+      </c>
+      <c r="E13">
+        <v>6.0642</v>
+      </c>
+      <c r="F13">
+        <v>8.3842</v>
+      </c>
+      <c r="G13">
+        <v>6.97</v>
+      </c>
+      <c r="H13">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.93</v>
+      </c>
+      <c r="K13">
+        <v>1.42</v>
+      </c>
+      <c r="L13">
+        <v>2.51</v>
+      </c>
+      <c r="M13">
+        <v>0.461131</v>
+      </c>
+      <c r="N13">
+        <v>2.048869</v>
+      </c>
+      <c r="O13">
+        <v>0.4097737999999999</v>
+      </c>
+      <c r="P13">
+        <v>1.6390952</v>
+      </c>
+      <c r="Q13">
+        <v>3.0590952</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1510250168633087</v>
+      </c>
+      <c r="T13">
+        <v>1.293941831141259</v>
+      </c>
+      <c r="U13">
+        <v>0.055</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.044</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>5.443138717631215</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1391000108876732</v>
+      </c>
+      <c r="C14">
+        <v>68.40777794584631</v>
+      </c>
+      <c r="D14">
+        <v>70.58417794584631</v>
+      </c>
+      <c r="E14">
+        <v>6.8264</v>
+      </c>
+      <c r="F14">
+        <v>9.1464</v>
+      </c>
+      <c r="G14">
+        <v>6.97</v>
+      </c>
+      <c r="H14">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.93</v>
+      </c>
+      <c r="K14">
+        <v>1.42</v>
+      </c>
+      <c r="L14">
+        <v>2.51</v>
+      </c>
+      <c r="M14">
+        <v>0.5030519999999999</v>
+      </c>
+      <c r="N14">
+        <v>2.006948</v>
+      </c>
+      <c r="O14">
+        <v>0.4013895999999999</v>
+      </c>
+      <c r="P14">
+        <v>1.6055584</v>
+      </c>
+      <c r="Q14">
+        <v>3.0255584</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1520681941905378</v>
+      </c>
+      <c r="T14">
+        <v>1.305969548478508</v>
+      </c>
+      <c r="U14">
+        <v>0.055</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.044</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>4.989543824495281</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1389477567670018</v>
+      </c>
+      <c r="C15">
+        <v>67.75288670935126</v>
+      </c>
+      <c r="D15">
+        <v>70.69148670935127</v>
+      </c>
+      <c r="E15">
+        <v>7.5886</v>
+      </c>
+      <c r="F15">
+        <v>9.9086</v>
+      </c>
+      <c r="G15">
+        <v>6.97</v>
+      </c>
+      <c r="H15">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.93</v>
+      </c>
+      <c r="K15">
+        <v>1.42</v>
+      </c>
+      <c r="L15">
+        <v>2.51</v>
+      </c>
+      <c r="M15">
+        <v>0.544973</v>
+      </c>
+      <c r="N15">
+        <v>1.965027</v>
+      </c>
+      <c r="O15">
+        <v>0.3930053999999998</v>
+      </c>
+      <c r="P15">
+        <v>1.5720216</v>
+      </c>
+      <c r="Q15">
+        <v>2.9920216</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1531353526057492</v>
+      </c>
+      <c r="T15">
+        <v>1.318273765064889</v>
+      </c>
+      <c r="U15">
+        <v>0.055</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.044</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>4.605732761072566</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1392211026463303</v>
+      </c>
+      <c r="C16">
+        <v>66.79826473741115</v>
+      </c>
+      <c r="D16">
+        <v>70.49906473741115</v>
+      </c>
+      <c r="E16">
+        <v>8.350800000000001</v>
+      </c>
+      <c r="F16">
+        <v>10.6708</v>
+      </c>
+      <c r="G16">
+        <v>6.97</v>
+      </c>
+      <c r="H16">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.93</v>
+      </c>
+      <c r="K16">
+        <v>1.42</v>
+      </c>
+      <c r="L16">
+        <v>2.51</v>
+      </c>
+      <c r="M16">
+        <v>0.6274430400000002</v>
+      </c>
+      <c r="N16">
+        <v>1.88255696</v>
+      </c>
+      <c r="O16">
+        <v>0.3765113919999998</v>
+      </c>
+      <c r="P16">
+        <v>1.506045568</v>
+      </c>
+      <c r="Q16">
+        <v>2.926045568</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1542273286585236</v>
+      </c>
+      <c r="T16">
+        <v>1.330864126223047</v>
+      </c>
+      <c r="U16">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.04704000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>4.00036312459534</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
         <v>0.15</v>
       </c>
-      <c r="AN3">
-        <v>-107.8947368421053</v>
-      </c>
-      <c r="AO3">
-        <v>-5.041493775933611</v>
-      </c>
-      <c r="AP3">
-        <v>-3.947368421052618</v>
-      </c>
-      <c r="AQ3">
-        <v>-16.20000000000001</v>
+      <c r="B17">
+        <v>0.1404552485256588</v>
+      </c>
+      <c r="C17">
+        <v>65.18017060991582</v>
+      </c>
+      <c r="D17">
+        <v>69.64317060991581</v>
+      </c>
+      <c r="E17">
+        <v>9.113</v>
+      </c>
+      <c r="F17">
+        <v>11.433</v>
+      </c>
+      <c r="G17">
+        <v>6.97</v>
+      </c>
+      <c r="H17">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.93</v>
+      </c>
+      <c r="K17">
+        <v>1.42</v>
+      </c>
+      <c r="L17">
+        <v>2.51</v>
+      </c>
+      <c r="M17">
+        <v>0.8014532999999999</v>
+      </c>
+      <c r="N17">
+        <v>1.7085467</v>
+      </c>
+      <c r="O17">
+        <v>0.3417093399999999</v>
+      </c>
+      <c r="P17">
+        <v>1.36683736</v>
+      </c>
+      <c r="Q17">
+        <v>2.78683736</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.155344998265481</v>
+      </c>
+      <c r="T17">
+        <v>1.343750731173161</v>
+      </c>
+      <c r="U17">
+        <v>0.0701</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.05608</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>3.131810674433557</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1431501944049874</v>
+      </c>
+      <c r="C18">
+        <v>62.61936758163435</v>
+      </c>
+      <c r="D18">
+        <v>67.84456758163435</v>
+      </c>
+      <c r="E18">
+        <v>9.8752</v>
+      </c>
+      <c r="F18">
+        <v>12.1952</v>
+      </c>
+      <c r="G18">
+        <v>6.97</v>
+      </c>
+      <c r="H18">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.93</v>
+      </c>
+      <c r="K18">
+        <v>1.42</v>
+      </c>
+      <c r="L18">
+        <v>2.51</v>
+      </c>
+      <c r="M18">
+        <v>1.11464128</v>
+      </c>
+      <c r="N18">
+        <v>1.39535872</v>
+      </c>
+      <c r="O18">
+        <v>0.2790717439999999</v>
+      </c>
+      <c r="P18">
+        <v>1.116286976</v>
+      </c>
+      <c r="Q18">
+        <v>2.536286976</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1564892790535564</v>
+      </c>
+      <c r="T18">
+        <v>1.356944160050659</v>
+      </c>
+      <c r="U18">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.07312</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>2.251845544424839</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1432891402843159</v>
+      </c>
+      <c r="C19">
+        <v>61.76695032963433</v>
+      </c>
+      <c r="D19">
+        <v>67.75435032963433</v>
+      </c>
+      <c r="E19">
+        <v>10.6374</v>
+      </c>
+      <c r="F19">
+        <v>12.9574</v>
+      </c>
+      <c r="G19">
+        <v>6.97</v>
+      </c>
+      <c r="H19">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.93</v>
+      </c>
+      <c r="K19">
+        <v>1.42</v>
+      </c>
+      <c r="L19">
+        <v>2.51</v>
+      </c>
+      <c r="M19">
+        <v>1.18430636</v>
+      </c>
+      <c r="N19">
+        <v>1.325693639999999</v>
+      </c>
+      <c r="O19">
+        <v>0.2651387279999998</v>
+      </c>
+      <c r="P19">
+        <v>1.060554912</v>
+      </c>
+      <c r="Q19">
+        <v>2.480554912</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1576611328726698</v>
+      </c>
+      <c r="T19">
+        <v>1.370455502877012</v>
+      </c>
+      <c r="U19">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.07312</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>2.119384041811613</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1434280861636445</v>
+      </c>
+      <c r="C20">
+        <v>60.9147726942778</v>
+      </c>
+      <c r="D20">
+        <v>67.6643726942778</v>
+      </c>
+      <c r="E20">
+        <v>11.3996</v>
+      </c>
+      <c r="F20">
+        <v>13.7196</v>
+      </c>
+      <c r="G20">
+        <v>6.97</v>
+      </c>
+      <c r="H20">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.93</v>
+      </c>
+      <c r="K20">
+        <v>1.42</v>
+      </c>
+      <c r="L20">
+        <v>2.51</v>
+      </c>
+      <c r="M20">
+        <v>1.25397144</v>
+      </c>
+      <c r="N20">
+        <v>1.25602856</v>
+      </c>
+      <c r="O20">
+        <v>0.2512057119999999</v>
+      </c>
+      <c r="P20">
+        <v>1.004822848</v>
+      </c>
+      <c r="Q20">
+        <v>2.424822848</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1588615684922494</v>
+      </c>
+      <c r="T20">
+        <v>1.38429639065035</v>
+      </c>
+      <c r="U20">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.07312</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>2.00164048393319</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.146774232042973</v>
+      </c>
+      <c r="C21">
+        <v>58.05563847595246</v>
+      </c>
+      <c r="D21">
+        <v>65.56743847595246</v>
+      </c>
+      <c r="E21">
+        <v>12.1618</v>
+      </c>
+      <c r="F21">
+        <v>14.4818</v>
+      </c>
+      <c r="G21">
+        <v>6.97</v>
+      </c>
+      <c r="H21">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.93</v>
+      </c>
+      <c r="K21">
+        <v>1.42</v>
+      </c>
+      <c r="L21">
+        <v>2.51</v>
+      </c>
+      <c r="M21">
+        <v>1.6292025</v>
+      </c>
+      <c r="N21">
+        <v>0.8807974999999997</v>
+      </c>
+      <c r="O21">
+        <v>0.1761594999999999</v>
+      </c>
+      <c r="P21">
+        <v>0.7046379999999998</v>
+      </c>
+      <c r="Q21">
+        <v>2.124638</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1600916444974976</v>
+      </c>
+      <c r="T21">
+        <v>1.398479028739079</v>
+      </c>
+      <c r="U21">
+        <v>0.1125</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>1.54063107563363</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1624795551372452</v>
+      </c>
+      <c r="C22">
+        <v>48.96742368243271</v>
+      </c>
+      <c r="D22">
+        <v>57.2414236824327</v>
+      </c>
+      <c r="E22">
+        <v>12.924</v>
+      </c>
+      <c r="F22">
+        <v>15.244</v>
+      </c>
+      <c r="G22">
+        <v>6.97</v>
+      </c>
+      <c r="H22">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.93</v>
+      </c>
+      <c r="K22">
+        <v>1.42</v>
+      </c>
+      <c r="L22">
+        <v>2.51</v>
+      </c>
+      <c r="M22">
+        <v>2.9969704</v>
+      </c>
+      <c r="N22">
+        <v>-0.4869704000000001</v>
+      </c>
+      <c r="O22">
+        <v>-0.09739408000000001</v>
+      </c>
+      <c r="P22">
+        <v>-0.3895763200000001</v>
+      </c>
+      <c r="Q22">
+        <v>1.03042368</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1621821912319737</v>
+      </c>
+      <c r="T22">
+        <v>1.422582797625024</v>
+      </c>
+      <c r="U22">
+        <v>0.1966</v>
+      </c>
+      <c r="V22">
+        <v>0.1675024885130663</v>
+      </c>
+      <c r="W22">
+        <v>0.1636690107583312</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.837512442565332</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1679447959530666</v>
+      </c>
+      <c r="C23">
+        <v>45.7828406297029</v>
+      </c>
+      <c r="D23">
+        <v>54.8190406297029</v>
+      </c>
+      <c r="E23">
+        <v>13.6862</v>
+      </c>
+      <c r="F23">
+        <v>16.0062</v>
+      </c>
+      <c r="G23">
+        <v>6.97</v>
+      </c>
+      <c r="H23">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.93</v>
+      </c>
+      <c r="K23">
+        <v>1.42</v>
+      </c>
+      <c r="L23">
+        <v>2.51</v>
+      </c>
+      <c r="M23">
+        <v>3.42212556</v>
+      </c>
+      <c r="N23">
+        <v>-0.9121255600000002</v>
+      </c>
+      <c r="O23">
+        <v>-0.182425112</v>
+      </c>
+      <c r="P23">
+        <v>-0.7297004480000002</v>
+      </c>
+      <c r="Q23">
+        <v>0.6902995520000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1640923972169625</v>
+      </c>
+      <c r="T23">
+        <v>1.444607257938395</v>
+      </c>
+      <c r="U23">
+        <v>0.2138</v>
+      </c>
+      <c r="V23">
+        <v>0.1466924550833839</v>
+      </c>
+      <c r="W23">
+        <v>0.1824371531031725</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.7334622754169196</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1696947959530666</v>
+      </c>
+      <c r="C24">
+        <v>44.28773661771775</v>
+      </c>
+      <c r="D24">
+        <v>54.08613661771776</v>
+      </c>
+      <c r="E24">
+        <v>14.4484</v>
+      </c>
+      <c r="F24">
+        <v>16.7684</v>
+      </c>
+      <c r="G24">
+        <v>6.97</v>
+      </c>
+      <c r="H24">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.93</v>
+      </c>
+      <c r="K24">
+        <v>1.42</v>
+      </c>
+      <c r="L24">
+        <v>2.51</v>
+      </c>
+      <c r="M24">
+        <v>3.58508392</v>
+      </c>
+      <c r="N24">
+        <v>-1.07508392</v>
+      </c>
+      <c r="O24">
+        <v>-0.2150167839999999</v>
+      </c>
+      <c r="P24">
+        <v>-0.8600671360000001</v>
+      </c>
+      <c r="Q24">
+        <v>0.5599328640000003</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1656987100017953</v>
+      </c>
+      <c r="T24">
+        <v>1.4631278638094</v>
+      </c>
+      <c r="U24">
+        <v>0.2138</v>
+      </c>
+      <c r="V24">
+        <v>0.1400246162159573</v>
+      </c>
+      <c r="W24">
+        <v>0.1838627370530283</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.7001230810797868</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1714447959530666</v>
+      </c>
+      <c r="C25">
+        <v>42.81197120114086</v>
+      </c>
+      <c r="D25">
+        <v>53.37257120114086</v>
+      </c>
+      <c r="E25">
+        <v>15.2106</v>
+      </c>
+      <c r="F25">
+        <v>17.5306</v>
+      </c>
+      <c r="G25">
+        <v>6.97</v>
+      </c>
+      <c r="H25">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.93</v>
+      </c>
+      <c r="K25">
+        <v>1.42</v>
+      </c>
+      <c r="L25">
+        <v>2.51</v>
+      </c>
+      <c r="M25">
+        <v>3.74804228</v>
+      </c>
+      <c r="N25">
+        <v>-1.23804228</v>
+      </c>
+      <c r="O25">
+        <v>-0.247608456</v>
+      </c>
+      <c r="P25">
+        <v>-0.9904338240000001</v>
+      </c>
+      <c r="Q25">
+        <v>0.4295661760000002</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1673467451966238</v>
+      </c>
+      <c r="T25">
+        <v>1.482129524378353</v>
+      </c>
+      <c r="U25">
+        <v>0.2138</v>
+      </c>
+      <c r="V25">
+        <v>0.1339365894239592</v>
+      </c>
+      <c r="W25">
+        <v>0.1851643571811575</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.669682947119796</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1731947959530666</v>
+      </c>
+      <c r="C26">
+        <v>41.35478893683792</v>
+      </c>
+      <c r="D26">
+        <v>52.67758893683792</v>
+      </c>
+      <c r="E26">
+        <v>15.9728</v>
+      </c>
+      <c r="F26">
+        <v>18.2928</v>
+      </c>
+      <c r="G26">
+        <v>6.97</v>
+      </c>
+      <c r="H26">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.93</v>
+      </c>
+      <c r="K26">
+        <v>1.42</v>
+      </c>
+      <c r="L26">
+        <v>2.51</v>
+      </c>
+      <c r="M26">
+        <v>3.91100064</v>
+      </c>
+      <c r="N26">
+        <v>-1.40100064</v>
+      </c>
+      <c r="O26">
+        <v>-0.2802001279999999</v>
+      </c>
+      <c r="P26">
+        <v>-1.120800512</v>
+      </c>
+      <c r="Q26">
+        <v>0.2991994880000004</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1690381497386847</v>
+      </c>
+      <c r="T26">
+        <v>1.501631228646489</v>
+      </c>
+      <c r="U26">
+        <v>0.2138</v>
+      </c>
+      <c r="V26">
+        <v>0.1283558981979609</v>
+      </c>
+      <c r="W26">
+        <v>0.1863575089652759</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.6417794909898046</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1749447959530666</v>
+      </c>
+      <c r="C27">
+        <v>39.91547322342317</v>
+      </c>
+      <c r="D27">
+        <v>52.00047322342317</v>
+      </c>
+      <c r="E27">
+        <v>16.735</v>
+      </c>
+      <c r="F27">
+        <v>19.055</v>
+      </c>
+      <c r="G27">
+        <v>6.97</v>
+      </c>
+      <c r="H27">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.93</v>
+      </c>
+      <c r="K27">
+        <v>1.42</v>
+      </c>
+      <c r="L27">
+        <v>2.51</v>
+      </c>
+      <c r="M27">
+        <v>4.073958999999999</v>
+      </c>
+      <c r="N27">
+        <v>-1.563959</v>
+      </c>
+      <c r="O27">
+        <v>-0.3127917999999998</v>
+      </c>
+      <c r="P27">
+        <v>-1.2511672</v>
+      </c>
+      <c r="Q27">
+        <v>0.1688328000000006</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1707746584018671</v>
+      </c>
+      <c r="T27">
+        <v>1.521652978361776</v>
+      </c>
+      <c r="U27">
+        <v>0.2138</v>
+      </c>
+      <c r="V27">
+        <v>0.1232216622700425</v>
+      </c>
+      <c r="W27">
+        <v>0.1874552086066649</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.6161083113502124</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1766947959530666</v>
+      </c>
+      <c r="C28">
+        <v>38.49334383658856</v>
+      </c>
+      <c r="D28">
+        <v>51.34054383658857</v>
+      </c>
+      <c r="E28">
+        <v>17.4972</v>
+      </c>
+      <c r="F28">
+        <v>19.8172</v>
+      </c>
+      <c r="G28">
+        <v>6.97</v>
+      </c>
+      <c r="H28">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.93</v>
+      </c>
+      <c r="K28">
+        <v>1.42</v>
+      </c>
+      <c r="L28">
+        <v>2.51</v>
+      </c>
+      <c r="M28">
+        <v>4.23691736</v>
+      </c>
+      <c r="N28">
+        <v>-1.72691736</v>
+      </c>
+      <c r="O28">
+        <v>-0.3453834719999999</v>
+      </c>
+      <c r="P28">
+        <v>-1.381533888</v>
+      </c>
+      <c r="Q28">
+        <v>0.0384661120000005</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1725580997316221</v>
+      </c>
+      <c r="T28">
+        <v>1.542215856447746</v>
+      </c>
+      <c r="U28">
+        <v>0.2138</v>
+      </c>
+      <c r="V28">
+        <v>0.1184823675673485</v>
+      </c>
+      <c r="W28">
+        <v>0.1884684698141009</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.5924118378367427</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1784447959530666</v>
+      </c>
+      <c r="C29">
+        <v>37.08775464975322</v>
+      </c>
+      <c r="D29">
+        <v>50.69715464975322</v>
+      </c>
+      <c r="E29">
+        <v>18.2594</v>
+      </c>
+      <c r="F29">
+        <v>20.5794</v>
+      </c>
+      <c r="G29">
+        <v>6.97</v>
+      </c>
+      <c r="H29">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.93</v>
+      </c>
+      <c r="K29">
+        <v>1.42</v>
+      </c>
+      <c r="L29">
+        <v>2.51</v>
+      </c>
+      <c r="M29">
+        <v>4.39987572</v>
+      </c>
+      <c r="N29">
+        <v>-1.88987572</v>
+      </c>
+      <c r="O29">
+        <v>-0.3779751439999999</v>
+      </c>
+      <c r="P29">
+        <v>-1.511900576</v>
+      </c>
+      <c r="Q29">
+        <v>-0.09190057599999979</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1743904024676717</v>
+      </c>
+      <c r="T29">
+        <v>1.563342101056619</v>
+      </c>
+      <c r="U29">
+        <v>0.2138</v>
+      </c>
+      <c r="V29">
+        <v>0.1140941317315208</v>
+      </c>
+      <c r="W29">
+        <v>0.1894066746358008</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.570470658657604</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1801947959530666</v>
+      </c>
+      <c r="C30">
+        <v>35.69809152397794</v>
+      </c>
+      <c r="D30">
+        <v>50.06969152397794</v>
+      </c>
+      <c r="E30">
+        <v>19.0216</v>
+      </c>
+      <c r="F30">
+        <v>21.3416</v>
+      </c>
+      <c r="G30">
+        <v>6.97</v>
+      </c>
+      <c r="H30">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.93</v>
+      </c>
+      <c r="K30">
+        <v>1.42</v>
+      </c>
+      <c r="L30">
+        <v>2.51</v>
+      </c>
+      <c r="M30">
+        <v>4.562834080000001</v>
+      </c>
+      <c r="N30">
+        <v>-2.052834080000001</v>
+      </c>
+      <c r="O30">
+        <v>-0.4105668160000001</v>
+      </c>
+      <c r="P30">
+        <v>-1.642267264000001</v>
+      </c>
+      <c r="Q30">
+        <v>-0.2222672640000005</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.176273602501945</v>
+      </c>
+      <c r="T30">
+        <v>1.585055185793516</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.1100193413125379</v>
+      </c>
+      <c r="W30">
+        <v>0.1902778648273794</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.5500967065626895</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1819447959530666</v>
+      </c>
+      <c r="C31">
+        <v>34.3237703526593</v>
+      </c>
+      <c r="D31">
+        <v>49.4575703526593</v>
+      </c>
+      <c r="E31">
+        <v>19.7838</v>
+      </c>
+      <c r="F31">
+        <v>22.1038</v>
+      </c>
+      <c r="G31">
+        <v>6.97</v>
+      </c>
+      <c r="H31">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.93</v>
+      </c>
+      <c r="K31">
+        <v>1.42</v>
+      </c>
+      <c r="L31">
+        <v>2.51</v>
+      </c>
+      <c r="M31">
+        <v>4.725792439999999</v>
+      </c>
+      <c r="N31">
+        <v>-2.21579244</v>
+      </c>
+      <c r="O31">
+        <v>-0.4431584879999998</v>
+      </c>
+      <c r="P31">
+        <v>-1.772633952</v>
+      </c>
+      <c r="Q31">
+        <v>-0.3526339519999993</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1782098504245075</v>
+      </c>
+      <c r="T31">
+        <v>1.607379906720186</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.1062255709224504</v>
+      </c>
+      <c r="W31">
+        <v>0.1910889729367801</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5311278546122521</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1836947959530666</v>
+      </c>
+      <c r="C32">
+        <v>32.96423524791758</v>
+      </c>
+      <c r="D32">
+        <v>48.86023524791758</v>
+      </c>
+      <c r="E32">
+        <v>20.546</v>
+      </c>
+      <c r="F32">
+        <v>22.866</v>
+      </c>
+      <c r="G32">
+        <v>6.97</v>
+      </c>
+      <c r="H32">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.93</v>
+      </c>
+      <c r="K32">
+        <v>1.42</v>
+      </c>
+      <c r="L32">
+        <v>2.51</v>
+      </c>
+      <c r="M32">
+        <v>4.8887508</v>
+      </c>
+      <c r="N32">
+        <v>-2.3787508</v>
+      </c>
+      <c r="O32">
+        <v>-0.4757501599999998</v>
+      </c>
+      <c r="P32">
+        <v>-1.90300064</v>
+      </c>
+      <c r="Q32">
+        <v>-0.4830006399999995</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1802014197162863</v>
+      </c>
+      <c r="T32">
+        <v>1.630342476816188</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.1026847185583687</v>
+      </c>
+      <c r="W32">
+        <v>0.1918460071722208</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.5134235927918437</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1935241580274312</v>
+      </c>
+      <c r="C33">
+        <v>29.09802777155912</v>
+      </c>
+      <c r="D33">
+        <v>45.75622777155913</v>
+      </c>
+      <c r="E33">
+        <v>21.3082</v>
+      </c>
+      <c r="F33">
+        <v>23.6282</v>
+      </c>
+      <c r="G33">
+        <v>6.97</v>
+      </c>
+      <c r="H33">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.93</v>
+      </c>
+      <c r="K33">
+        <v>1.42</v>
+      </c>
+      <c r="L33">
+        <v>2.51</v>
+      </c>
+      <c r="M33">
+        <v>5.64241416</v>
+      </c>
+      <c r="N33">
+        <v>-3.132414160000001</v>
+      </c>
+      <c r="O33">
+        <v>-0.626482832</v>
+      </c>
+      <c r="P33">
+        <v>-2.505931328000001</v>
+      </c>
+      <c r="Q33">
+        <v>-1.085931328</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1827280519938622</v>
+      </c>
+      <c r="T33">
+        <v>1.659474263001165</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.08896900967652467</v>
+      </c>
+      <c r="W33">
+        <v>0.2175542004892459</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.4448450483826234</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1955241580274311</v>
+      </c>
+      <c r="C34">
+        <v>27.75191998928156</v>
+      </c>
+      <c r="D34">
+        <v>45.17231998928156</v>
+      </c>
+      <c r="E34">
+        <v>22.0704</v>
+      </c>
+      <c r="F34">
+        <v>24.3904</v>
+      </c>
+      <c r="G34">
+        <v>6.97</v>
+      </c>
+      <c r="H34">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.93</v>
+      </c>
+      <c r="K34">
+        <v>1.42</v>
+      </c>
+      <c r="L34">
+        <v>2.51</v>
+      </c>
+      <c r="M34">
+        <v>5.82442752</v>
+      </c>
+      <c r="N34">
+        <v>-3.314427520000001</v>
+      </c>
+      <c r="O34">
+        <v>-0.662885504</v>
+      </c>
+      <c r="P34">
+        <v>-2.651542016000001</v>
+      </c>
+      <c r="Q34">
+        <v>-1.231542016</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.184844640993772</v>
+      </c>
+      <c r="T34">
+        <v>1.683878296280594</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.08618872812413328</v>
+      </c>
+      <c r="W34">
+        <v>0.218218131723957</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.4309436406206665</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1975241580274312</v>
+      </c>
+      <c r="C35">
+        <v>26.42052723941074</v>
+      </c>
+      <c r="D35">
+        <v>44.60312723941074</v>
+      </c>
+      <c r="E35">
+        <v>22.8326</v>
+      </c>
+      <c r="F35">
+        <v>25.1526</v>
+      </c>
+      <c r="G35">
+        <v>6.97</v>
+      </c>
+      <c r="H35">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.93</v>
+      </c>
+      <c r="K35">
+        <v>1.42</v>
+      </c>
+      <c r="L35">
+        <v>2.51</v>
+      </c>
+      <c r="M35">
+        <v>6.00644088</v>
+      </c>
+      <c r="N35">
+        <v>-3.496440880000001</v>
+      </c>
+      <c r="O35">
+        <v>-0.6992881759999999</v>
+      </c>
+      <c r="P35">
+        <v>-2.797152704000001</v>
+      </c>
+      <c r="Q35">
+        <v>-1.377152704</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1870244117548731</v>
+      </c>
+      <c r="T35">
+        <v>1.709010808165379</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.08357694848400803</v>
+      </c>
+      <c r="W35">
+        <v>0.2188418247020189</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.4178847424200403</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1995241580274312</v>
+      </c>
+      <c r="C36">
+        <v>25.10330019448078</v>
+      </c>
+      <c r="D36">
+        <v>44.04810019448078</v>
+      </c>
+      <c r="E36">
+        <v>23.5948</v>
+      </c>
+      <c r="F36">
+        <v>25.9148</v>
+      </c>
+      <c r="G36">
+        <v>6.97</v>
+      </c>
+      <c r="H36">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.93</v>
+      </c>
+      <c r="K36">
+        <v>1.42</v>
+      </c>
+      <c r="L36">
+        <v>2.51</v>
+      </c>
+      <c r="M36">
+        <v>6.188454240000001</v>
+      </c>
+      <c r="N36">
+        <v>-3.678454240000002</v>
+      </c>
+      <c r="O36">
+        <v>-0.7356908480000002</v>
+      </c>
+      <c r="P36">
+        <v>-2.942763392000002</v>
+      </c>
+      <c r="Q36">
+        <v>-1.522763392000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1892702361754015</v>
+      </c>
+      <c r="T36">
+        <v>1.7349049113194</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.08111880294036072</v>
+      </c>
+      <c r="W36">
+        <v>0.2194288298578419</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.4055940147018037</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2015241580274312</v>
+      </c>
+      <c r="C37">
+        <v>23.79971653358568</v>
+      </c>
+      <c r="D37">
+        <v>43.50671653358568</v>
+      </c>
+      <c r="E37">
+        <v>24.357</v>
+      </c>
+      <c r="F37">
+        <v>26.677</v>
+      </c>
+      <c r="G37">
+        <v>6.97</v>
+      </c>
+      <c r="H37">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.93</v>
+      </c>
+      <c r="K37">
+        <v>1.42</v>
+      </c>
+      <c r="L37">
+        <v>2.51</v>
+      </c>
+      <c r="M37">
+        <v>6.370467600000001</v>
+      </c>
+      <c r="N37">
+        <v>-3.860467600000002</v>
+      </c>
+      <c r="O37">
+        <v>-0.7720935200000001</v>
+      </c>
+      <c r="P37">
+        <v>-3.088374080000001</v>
+      </c>
+      <c r="Q37">
+        <v>-1.668374080000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1915851628857922</v>
+      </c>
+      <c r="T37">
+        <v>1.761595756108929</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.07880112285635041</v>
+      </c>
+      <c r="W37">
+        <v>0.2199822918619035</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3940056142817522</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2035241580274312</v>
+      </c>
+      <c r="C38">
+        <v>22.50927930287735</v>
+      </c>
+      <c r="D38">
+        <v>42.97847930287735</v>
+      </c>
+      <c r="E38">
+        <v>25.1192</v>
+      </c>
+      <c r="F38">
+        <v>27.4392</v>
+      </c>
+      <c r="G38">
+        <v>6.97</v>
+      </c>
+      <c r="H38">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.93</v>
+      </c>
+      <c r="K38">
+        <v>1.42</v>
+      </c>
+      <c r="L38">
+        <v>2.51</v>
+      </c>
+      <c r="M38">
+        <v>6.55248096</v>
+      </c>
+      <c r="N38">
+        <v>-4.042480960000001</v>
+      </c>
+      <c r="O38">
+        <v>-0.808496192</v>
+      </c>
+      <c r="P38">
+        <v>-3.233984768000001</v>
+      </c>
+      <c r="Q38">
+        <v>-1.813984768000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1939724310558827</v>
+      </c>
+      <c r="T38">
+        <v>1.789120689798131</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.07661220277700735</v>
+      </c>
+      <c r="W38">
+        <v>0.2205050059768507</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3830610138850369</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2055241580274312</v>
+      </c>
+      <c r="C39">
+        <v>21.2315153940669</v>
+      </c>
+      <c r="D39">
+        <v>42.4629153940669</v>
+      </c>
+      <c r="E39">
+        <v>25.8814</v>
+      </c>
+      <c r="F39">
+        <v>28.2014</v>
+      </c>
+      <c r="G39">
+        <v>6.97</v>
+      </c>
+      <c r="H39">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.93</v>
+      </c>
+      <c r="K39">
+        <v>1.42</v>
+      </c>
+      <c r="L39">
+        <v>2.51</v>
+      </c>
+      <c r="M39">
+        <v>6.73449432</v>
+      </c>
+      <c r="N39">
+        <v>-4.224494320000001</v>
+      </c>
+      <c r="O39">
+        <v>-0.8448988639999999</v>
+      </c>
+      <c r="P39">
+        <v>-3.379595456000001</v>
+      </c>
+      <c r="Q39">
+        <v>-1.959595456</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1964354855170872</v>
+      </c>
+      <c r="T39">
+        <v>1.817519430906038</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.07454160270195309</v>
+      </c>
+      <c r="W39">
+        <v>0.2209994652747736</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.3727080135097656</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2075241580274312</v>
+      </c>
+      <c r="C40">
+        <v>19.96597413113805</v>
+      </c>
+      <c r="D40">
+        <v>41.95957413113806</v>
+      </c>
+      <c r="E40">
+        <v>26.6436</v>
+      </c>
+      <c r="F40">
+        <v>28.9636</v>
+      </c>
+      <c r="G40">
+        <v>6.97</v>
+      </c>
+      <c r="H40">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.93</v>
+      </c>
+      <c r="K40">
+        <v>1.42</v>
+      </c>
+      <c r="L40">
+        <v>2.51</v>
+      </c>
+      <c r="M40">
+        <v>6.91650768</v>
+      </c>
+      <c r="N40">
+        <v>-4.406507680000001</v>
+      </c>
+      <c r="O40">
+        <v>-0.8813015359999999</v>
+      </c>
+      <c r="P40">
+        <v>-3.525206144000001</v>
+      </c>
+      <c r="Q40">
+        <v>-2.105206144</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1989779933480079</v>
+      </c>
+      <c r="T40">
+        <v>1.84683426043678</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.07257998157821749</v>
+      </c>
+      <c r="W40">
+        <v>0.2214679003991217</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.3628999078910875</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2095241580274312</v>
+      </c>
+      <c r="C41">
+        <v>18.71222595639881</v>
+      </c>
+      <c r="D41">
+        <v>41.46802595639881</v>
+      </c>
+      <c r="E41">
+        <v>27.4058</v>
+      </c>
+      <c r="F41">
+        <v>29.7258</v>
+      </c>
+      <c r="G41">
+        <v>6.97</v>
+      </c>
+      <c r="H41">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.93</v>
+      </c>
+      <c r="K41">
+        <v>1.42</v>
+      </c>
+      <c r="L41">
+        <v>2.51</v>
+      </c>
+      <c r="M41">
+        <v>7.098521040000001</v>
+      </c>
+      <c r="N41">
+        <v>-4.588521040000001</v>
+      </c>
+      <c r="O41">
+        <v>-0.917704208</v>
+      </c>
+      <c r="P41">
+        <v>-3.670816832000001</v>
+      </c>
+      <c r="Q41">
+        <v>-2.250816832</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2016038620914179</v>
+      </c>
+      <c r="T41">
+        <v>1.87711023191935</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.07071895640954524</v>
+      </c>
+      <c r="W41">
+        <v>0.2219123132094006</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3535947820477263</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2115241580274312</v>
+      </c>
+      <c r="C42">
+        <v>17.46986120781961</v>
+      </c>
+      <c r="D42">
+        <v>40.98786120781961</v>
+      </c>
+      <c r="E42">
+        <v>28.168</v>
+      </c>
+      <c r="F42">
+        <v>30.488</v>
+      </c>
+      <c r="G42">
+        <v>6.97</v>
+      </c>
+      <c r="H42">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.93</v>
+      </c>
+      <c r="K42">
+        <v>1.42</v>
+      </c>
+      <c r="L42">
+        <v>2.51</v>
+      </c>
+      <c r="M42">
+        <v>7.280534400000001</v>
+      </c>
+      <c r="N42">
+        <v>-4.770534400000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.9541068799999999</v>
+      </c>
+      <c r="P42">
+        <v>-3.816427520000001</v>
+      </c>
+      <c r="Q42">
+        <v>-2.39642752</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2043172597929416</v>
+      </c>
+      <c r="T42">
+        <v>1.90839540245134</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.06895098249930662</v>
+      </c>
+      <c r="W42">
+        <v>0.2223345053791656</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3447549124965331</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2135241580274312</v>
+      </c>
+      <c r="C43">
+        <v>16.23848898034337</v>
+      </c>
+      <c r="D43">
+        <v>40.51868898034337</v>
+      </c>
+      <c r="E43">
+        <v>28.9302</v>
+      </c>
+      <c r="F43">
+        <v>31.2502</v>
+      </c>
+      <c r="G43">
+        <v>6.97</v>
+      </c>
+      <c r="H43">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.93</v>
+      </c>
+      <c r="K43">
+        <v>1.42</v>
+      </c>
+      <c r="L43">
+        <v>2.51</v>
+      </c>
+      <c r="M43">
+        <v>7.462547760000001</v>
+      </c>
+      <c r="N43">
+        <v>-4.952547760000002</v>
+      </c>
+      <c r="O43">
+        <v>-0.9905095520000001</v>
+      </c>
+      <c r="P43">
+        <v>-3.962038208000001</v>
+      </c>
+      <c r="Q43">
+        <v>-2.542038208000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2071226370775677</v>
+      </c>
+      <c r="T43">
+        <v>1.94074108723865</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.06726925121883572</v>
+      </c>
+      <c r="W43">
+        <v>0.222736102808942</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3363462560941787</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2155241580274312</v>
+      </c>
+      <c r="C44">
+        <v>15.0177360645156</v>
+      </c>
+      <c r="D44">
+        <v>40.0601360645156</v>
+      </c>
+      <c r="E44">
+        <v>29.6924</v>
+      </c>
+      <c r="F44">
+        <v>32.0124</v>
+      </c>
+      <c r="G44">
+        <v>6.97</v>
+      </c>
+      <c r="H44">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.93</v>
+      </c>
+      <c r="K44">
+        <v>1.42</v>
+      </c>
+      <c r="L44">
+        <v>2.51</v>
+      </c>
+      <c r="M44">
+        <v>7.644561120000001</v>
+      </c>
+      <c r="N44">
+        <v>-5.134561120000001</v>
+      </c>
+      <c r="O44">
+        <v>-1.026912224</v>
+      </c>
+      <c r="P44">
+        <v>-4.107648896000001</v>
+      </c>
+      <c r="Q44">
+        <v>-2.687648896</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2100247515099395</v>
+      </c>
+      <c r="T44">
+        <v>1.974202140466903</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.06566760238029203</v>
+      </c>
+      <c r="W44">
+        <v>0.2231185765515863</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3283380119014602</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2175241580274312</v>
+      </c>
+      <c r="C45">
+        <v>13.80724595637736</v>
+      </c>
+      <c r="D45">
+        <v>39.61184595637737</v>
+      </c>
+      <c r="E45">
+        <v>30.4546</v>
+      </c>
+      <c r="F45">
+        <v>32.7746</v>
+      </c>
+      <c r="G45">
+        <v>6.97</v>
+      </c>
+      <c r="H45">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.93</v>
+      </c>
+      <c r="K45">
+        <v>1.42</v>
+      </c>
+      <c r="L45">
+        <v>2.51</v>
+      </c>
+      <c r="M45">
+        <v>7.826574480000001</v>
+      </c>
+      <c r="N45">
+        <v>-5.316574480000001</v>
+      </c>
+      <c r="O45">
+        <v>-1.063314896</v>
+      </c>
+      <c r="P45">
+        <v>-4.253259584000001</v>
+      </c>
+      <c r="Q45">
+        <v>-2.833259584000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2130286945188858</v>
+      </c>
+      <c r="T45">
+        <v>2.008837265738252</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.06414044883656429</v>
+      </c>
+      <c r="W45">
+        <v>0.2234832608178285</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3207022441828216</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2195241580274312</v>
+      </c>
+      <c r="C46">
+        <v>12.60667793310109</v>
+      </c>
+      <c r="D46">
+        <v>39.17347793310109</v>
+      </c>
+      <c r="E46">
+        <v>31.2168</v>
+      </c>
+      <c r="F46">
+        <v>33.5368</v>
+      </c>
+      <c r="G46">
+        <v>6.97</v>
+      </c>
+      <c r="H46">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.93</v>
+      </c>
+      <c r="K46">
+        <v>1.42</v>
+      </c>
+      <c r="L46">
+        <v>2.51</v>
+      </c>
+      <c r="M46">
+        <v>8.008587840000001</v>
+      </c>
+      <c r="N46">
+        <v>-5.498587840000001</v>
+      </c>
+      <c r="O46">
+        <v>-1.099717568</v>
+      </c>
+      <c r="P46">
+        <v>-4.398870272000001</v>
+      </c>
+      <c r="Q46">
+        <v>-2.978870272</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2161399212067231</v>
+      </c>
+      <c r="T46">
+        <v>2.044709359769293</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.06268271136300602</v>
+      </c>
+      <c r="W46">
+        <v>0.2238313685265142</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3134135568150301</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2215241580274312</v>
+      </c>
+      <c r="C47">
+        <v>11.41570618933176</v>
+      </c>
+      <c r="D47">
+        <v>38.74470618933177</v>
+      </c>
+      <c r="E47">
+        <v>31.979</v>
+      </c>
+      <c r="F47">
+        <v>34.299</v>
+      </c>
+      <c r="G47">
+        <v>6.97</v>
+      </c>
+      <c r="H47">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.93</v>
+      </c>
+      <c r="K47">
+        <v>1.42</v>
+      </c>
+      <c r="L47">
+        <v>2.51</v>
+      </c>
+      <c r="M47">
+        <v>8.1906012</v>
+      </c>
+      <c r="N47">
+        <v>-5.6806012</v>
+      </c>
+      <c r="O47">
+        <v>-1.13612024</v>
+      </c>
+      <c r="P47">
+        <v>-4.54448096</v>
+      </c>
+      <c r="Q47">
+        <v>-3.12448096</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2193642834104817</v>
+      </c>
+      <c r="T47">
+        <v>2.08188589358328</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.06128976222160589</v>
+      </c>
+      <c r="W47">
+        <v>0.2241640047814805</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3064488111080295</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2235241580274312</v>
+      </c>
+      <c r="C48">
+        <v>10.23401902963305</v>
+      </c>
+      <c r="D48">
+        <v>38.32521902963305</v>
+      </c>
+      <c r="E48">
+        <v>32.7412</v>
+      </c>
+      <c r="F48">
+        <v>35.0612</v>
+      </c>
+      <c r="G48">
+        <v>6.97</v>
+      </c>
+      <c r="H48">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.93</v>
+      </c>
+      <c r="K48">
+        <v>1.42</v>
+      </c>
+      <c r="L48">
+        <v>2.51</v>
+      </c>
+      <c r="M48">
+        <v>8.372614560000001</v>
+      </c>
+      <c r="N48">
+        <v>-5.862614560000001</v>
+      </c>
+      <c r="O48">
+        <v>-1.172522912</v>
+      </c>
+      <c r="P48">
+        <v>-4.690091648000001</v>
+      </c>
+      <c r="Q48">
+        <v>-3.270091648000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2227080664366017</v>
+      </c>
+      <c r="T48">
+        <v>2.120439336057044</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.05995737608635358</v>
+      </c>
+      <c r="W48">
+        <v>0.2244821785905788</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2997868804317679</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2255241580274312</v>
+      </c>
+      <c r="C49">
+        <v>9.061318112831465</v>
+      </c>
+      <c r="D49">
+        <v>37.91471811283147</v>
+      </c>
+      <c r="E49">
+        <v>33.5034</v>
+      </c>
+      <c r="F49">
+        <v>35.8234</v>
+      </c>
+      <c r="G49">
+        <v>6.97</v>
+      </c>
+      <c r="H49">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.93</v>
+      </c>
+      <c r="K49">
+        <v>1.42</v>
+      </c>
+      <c r="L49">
+        <v>2.51</v>
+      </c>
+      <c r="M49">
+        <v>8.55462792</v>
+      </c>
+      <c r="N49">
+        <v>-6.04462792</v>
+      </c>
+      <c r="O49">
+        <v>-1.208925584</v>
+      </c>
+      <c r="P49">
+        <v>-4.835702336000001</v>
+      </c>
+      <c r="Q49">
+        <v>-3.415702336</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2261780299542735</v>
+      </c>
+      <c r="T49">
+        <v>2.160447625416611</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.05868168723345245</v>
+      </c>
+      <c r="W49">
+        <v>0.2247868130886516</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2934084361672623</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2275241580274311</v>
+      </c>
+      <c r="C50">
+        <v>7.897317744408895</v>
+      </c>
+      <c r="D50">
+        <v>37.5129177444089</v>
+      </c>
+      <c r="E50">
+        <v>34.2656</v>
+      </c>
+      <c r="F50">
+        <v>36.5856</v>
+      </c>
+      <c r="G50">
+        <v>6.97</v>
+      </c>
+      <c r="H50">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.93</v>
+      </c>
+      <c r="K50">
+        <v>1.42</v>
+      </c>
+      <c r="L50">
+        <v>2.51</v>
+      </c>
+      <c r="M50">
+        <v>8.736641280000001</v>
+      </c>
+      <c r="N50">
+        <v>-6.226641280000001</v>
+      </c>
+      <c r="O50">
+        <v>-1.245328256</v>
+      </c>
+      <c r="P50">
+        <v>-4.981313024000001</v>
+      </c>
+      <c r="Q50">
+        <v>-3.561313024000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2297814536072402</v>
+      </c>
+      <c r="T50">
+        <v>2.201994695136161</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05745915208275552</v>
+      </c>
+      <c r="W50">
+        <v>0.225078754482638</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2872957604137777</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2295241580274312</v>
+      </c>
+      <c r="C51">
+        <v>6.741744213416403</v>
+      </c>
+      <c r="D51">
+        <v>37.1195442134164</v>
+      </c>
+      <c r="E51">
+        <v>35.0278</v>
+      </c>
+      <c r="F51">
+        <v>37.3478</v>
+      </c>
+      <c r="G51">
+        <v>6.97</v>
+      </c>
+      <c r="H51">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.93</v>
+      </c>
+      <c r="K51">
+        <v>1.42</v>
+      </c>
+      <c r="L51">
+        <v>2.51</v>
+      </c>
+      <c r="M51">
+        <v>8.91865464</v>
+      </c>
+      <c r="N51">
+        <v>-6.40865464</v>
+      </c>
+      <c r="O51">
+        <v>-1.281730928</v>
+      </c>
+      <c r="P51">
+        <v>-5.126923712</v>
+      </c>
+      <c r="Q51">
+        <v>-3.706923712</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2335261879916959</v>
+      </c>
+      <c r="T51">
+        <v>2.245171061707458</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.0562865163259646</v>
+      </c>
+      <c r="W51">
+        <v>0.2253587799013597</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.281432581629823</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2315241580274311</v>
+      </c>
+      <c r="C52">
+        <v>5.594335170675308</v>
+      </c>
+      <c r="D52">
+        <v>36.73433517067531</v>
+      </c>
+      <c r="E52">
+        <v>35.79</v>
+      </c>
+      <c r="F52">
+        <v>38.11</v>
+      </c>
+      <c r="G52">
+        <v>6.97</v>
+      </c>
+      <c r="H52">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.93</v>
+      </c>
+      <c r="K52">
+        <v>1.42</v>
+      </c>
+      <c r="L52">
+        <v>2.51</v>
+      </c>
+      <c r="M52">
+        <v>9.100668000000001</v>
+      </c>
+      <c r="N52">
+        <v>-6.590668000000001</v>
+      </c>
+      <c r="O52">
+        <v>-1.3181336</v>
+      </c>
+      <c r="P52">
+        <v>-5.272534400000001</v>
+      </c>
+      <c r="Q52">
+        <v>-3.852534400000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2374207117515298</v>
+      </c>
+      <c r="T52">
+        <v>2.290074482941607</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.05516078599944529</v>
+      </c>
+      <c r="W52">
+        <v>0.2256276043033325</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2758039299972266</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2335241580274312</v>
+      </c>
+      <c r="C53">
+        <v>4.454839045296751</v>
+      </c>
+      <c r="D53">
+        <v>36.35703904529675</v>
+      </c>
+      <c r="E53">
+        <v>36.5522</v>
+      </c>
+      <c r="F53">
+        <v>38.8722</v>
+      </c>
+      <c r="G53">
+        <v>6.97</v>
+      </c>
+      <c r="H53">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.93</v>
+      </c>
+      <c r="K53">
+        <v>1.42</v>
+      </c>
+      <c r="L53">
+        <v>2.51</v>
+      </c>
+      <c r="M53">
+        <v>9.28268136</v>
+      </c>
+      <c r="N53">
+        <v>-6.77268136</v>
+      </c>
+      <c r="O53">
+        <v>-1.354536272</v>
+      </c>
+      <c r="P53">
+        <v>-5.418145088</v>
+      </c>
+      <c r="Q53">
+        <v>-3.998145088</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2414741956648264</v>
+      </c>
+      <c r="T53">
+        <v>2.336810696879192</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.05407920196024048</v>
+      </c>
+      <c r="W53">
+        <v>0.2258858865718946</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2703960098012025</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2355241580274312</v>
+      </c>
+      <c r="C54">
+        <v>3.323014496793384</v>
+      </c>
+      <c r="D54">
+        <v>35.98741449679338</v>
+      </c>
+      <c r="E54">
+        <v>37.3144</v>
+      </c>
+      <c r="F54">
+        <v>39.6344</v>
+      </c>
+      <c r="G54">
+        <v>6.97</v>
+      </c>
+      <c r="H54">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.93</v>
+      </c>
+      <c r="K54">
+        <v>1.42</v>
+      </c>
+      <c r="L54">
+        <v>2.51</v>
+      </c>
+      <c r="M54">
+        <v>9.464694720000001</v>
+      </c>
+      <c r="N54">
+        <v>-6.954694720000001</v>
+      </c>
+      <c r="O54">
+        <v>-1.390938944</v>
+      </c>
+      <c r="P54">
+        <v>-5.563755776000001</v>
+      </c>
+      <c r="Q54">
+        <v>-4.143755776000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.245696574741177</v>
+      </c>
+      <c r="T54">
+        <v>2.385494253064175</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.05303921730715894</v>
+      </c>
+      <c r="W54">
+        <v>0.2261342349070505</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2651960865357947</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2375241580274312</v>
+      </c>
+      <c r="C55">
+        <v>2.198629900275172</v>
+      </c>
+      <c r="D55">
+        <v>35.62522990027517</v>
+      </c>
+      <c r="E55">
+        <v>38.0766</v>
+      </c>
+      <c r="F55">
+        <v>40.3966</v>
+      </c>
+      <c r="G55">
+        <v>6.97</v>
+      </c>
+      <c r="H55">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.93</v>
+      </c>
+      <c r="K55">
+        <v>1.42</v>
+      </c>
+      <c r="L55">
+        <v>2.51</v>
+      </c>
+      <c r="M55">
+        <v>9.64670808</v>
+      </c>
+      <c r="N55">
+        <v>-7.13670808</v>
+      </c>
+      <c r="O55">
+        <v>-1.427341616</v>
+      </c>
+      <c r="P55">
+        <v>-5.709366464</v>
+      </c>
+      <c r="Q55">
+        <v>-4.289366464</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2500986295229041</v>
+      </c>
+      <c r="T55">
+        <v>2.43624944993788</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.05203847735796726</v>
+      </c>
+      <c r="W55">
+        <v>0.2263732116069174</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2601923867898364</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2395241580274312</v>
+      </c>
+      <c r="C56">
+        <v>1.081462862422093</v>
+      </c>
+      <c r="D56">
+        <v>35.27026286242209</v>
+      </c>
+      <c r="E56">
+        <v>38.8388</v>
+      </c>
+      <c r="F56">
+        <v>41.1588</v>
+      </c>
+      <c r="G56">
+        <v>6.97</v>
+      </c>
+      <c r="H56">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.93</v>
+      </c>
+      <c r="K56">
+        <v>1.42</v>
+      </c>
+      <c r="L56">
+        <v>2.51</v>
+      </c>
+      <c r="M56">
+        <v>9.828721440000001</v>
+      </c>
+      <c r="N56">
+        <v>-7.318721440000001</v>
+      </c>
+      <c r="O56">
+        <v>-1.463744288</v>
+      </c>
+      <c r="P56">
+        <v>-5.854977152000001</v>
+      </c>
+      <c r="Q56">
+        <v>-4.434977152</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2546920779907934</v>
+      </c>
+      <c r="T56">
+        <v>2.489211394501747</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.05107480185133824</v>
+      </c>
+      <c r="W56">
+        <v>0.2266033373179004</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2553740092566912</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2415241580274312</v>
+      </c>
+      <c r="C57">
+        <v>-0.02870023389176168</v>
+      </c>
+      <c r="D57">
+        <v>34.92229976610824</v>
+      </c>
+      <c r="E57">
+        <v>39.601</v>
+      </c>
+      <c r="F57">
+        <v>41.921</v>
+      </c>
+      <c r="G57">
+        <v>6.97</v>
+      </c>
+      <c r="H57">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.93</v>
+      </c>
+      <c r="K57">
+        <v>1.42</v>
+      </c>
+      <c r="L57">
+        <v>2.51</v>
+      </c>
+      <c r="M57">
+        <v>10.0107348</v>
+      </c>
+      <c r="N57">
+        <v>-7.5007348</v>
+      </c>
+      <c r="O57">
+        <v>-1.50014696</v>
+      </c>
+      <c r="P57">
+        <v>-6.000587840000001</v>
+      </c>
+      <c r="Q57">
+        <v>-4.58058784</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2594896797239221</v>
+      </c>
+      <c r="T57">
+        <v>2.544527203268453</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.05014616909040481</v>
+      </c>
+      <c r="W57">
+        <v>0.2268250948212114</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2507308454520242</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2435241580274312</v>
+      </c>
+      <c r="C58">
+        <v>-1.132064658282069</v>
+      </c>
+      <c r="D58">
+        <v>34.58113534171794</v>
+      </c>
+      <c r="E58">
+        <v>40.36320000000001</v>
+      </c>
+      <c r="F58">
+        <v>42.68320000000001</v>
+      </c>
+      <c r="G58">
+        <v>6.97</v>
+      </c>
+      <c r="H58">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.93</v>
+      </c>
+      <c r="K58">
+        <v>1.42</v>
+      </c>
+      <c r="L58">
+        <v>2.51</v>
+      </c>
+      <c r="M58">
+        <v>10.19274816</v>
+      </c>
+      <c r="N58">
+        <v>-7.682748160000003</v>
+      </c>
+      <c r="O58">
+        <v>-1.536549632</v>
+      </c>
+      <c r="P58">
+        <v>-6.146198528000003</v>
+      </c>
+      <c r="Q58">
+        <v>-4.726198528000003</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2645053542631022</v>
+      </c>
+      <c r="T58">
+        <v>2.6023573669791</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.049250701785219</v>
+      </c>
+      <c r="W58">
+        <v>0.2270389324136897</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2462535089260951</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2455241580274312</v>
+      </c>
+      <c r="C59">
+        <v>-2.228827736653678</v>
+      </c>
+      <c r="D59">
+        <v>34.24657226334633</v>
+      </c>
+      <c r="E59">
+        <v>41.12540000000001</v>
+      </c>
+      <c r="F59">
+        <v>43.44540000000001</v>
+      </c>
+      <c r="G59">
+        <v>6.97</v>
+      </c>
+      <c r="H59">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.93</v>
+      </c>
+      <c r="K59">
+        <v>1.42</v>
+      </c>
+      <c r="L59">
+        <v>2.51</v>
+      </c>
+      <c r="M59">
+        <v>10.37476152</v>
+      </c>
+      <c r="N59">
+        <v>-7.864761520000002</v>
+      </c>
+      <c r="O59">
+        <v>-1.572952304</v>
+      </c>
+      <c r="P59">
+        <v>-6.291809216000002</v>
+      </c>
+      <c r="Q59">
+        <v>-4.871809216000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2697543159901511</v>
+      </c>
+      <c r="T59">
+        <v>2.662877305746056</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04838665438547832</v>
+      </c>
+      <c r="W59">
+        <v>0.2272452669327478</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2419332719273917</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2475241580274312</v>
+      </c>
+      <c r="C60">
+        <v>-3.319179231784815</v>
+      </c>
+      <c r="D60">
+        <v>33.91842076821519</v>
+      </c>
+      <c r="E60">
+        <v>41.8876</v>
+      </c>
+      <c r="F60">
+        <v>44.2076</v>
+      </c>
+      <c r="G60">
+        <v>6.97</v>
+      </c>
+      <c r="H60">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.93</v>
+      </c>
+      <c r="K60">
+        <v>1.42</v>
+      </c>
+      <c r="L60">
+        <v>2.51</v>
+      </c>
+      <c r="M60">
+        <v>10.55677488</v>
+      </c>
+      <c r="N60">
+        <v>-8.046774880000001</v>
+      </c>
+      <c r="O60">
+        <v>-1.609354976</v>
+      </c>
+      <c r="P60">
+        <v>-6.437419904000001</v>
+      </c>
+      <c r="Q60">
+        <v>-5.017419904</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2752532282756308</v>
+      </c>
+      <c r="T60">
+        <v>2.726279146359056</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04755240172365974</v>
+      </c>
+      <c r="W60">
+        <v>0.2274444864683901</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2377620086182988</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2495241580274312</v>
+      </c>
+      <c r="C61">
+        <v>-4.403301702238345</v>
+      </c>
+      <c r="D61">
+        <v>33.59649829776166</v>
+      </c>
+      <c r="E61">
+        <v>42.6498</v>
+      </c>
+      <c r="F61">
+        <v>44.9698</v>
+      </c>
+      <c r="G61">
+        <v>6.97</v>
+      </c>
+      <c r="H61">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.93</v>
+      </c>
+      <c r="K61">
+        <v>1.42</v>
+      </c>
+      <c r="L61">
+        <v>2.51</v>
+      </c>
+      <c r="M61">
+        <v>10.73878824</v>
+      </c>
+      <c r="N61">
+        <v>-8.22878824</v>
+      </c>
+      <c r="O61">
+        <v>-1.645757648</v>
+      </c>
+      <c r="P61">
+        <v>-6.583030592</v>
+      </c>
+      <c r="Q61">
+        <v>-5.163030592</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2810203801847925</v>
+      </c>
+      <c r="T61">
+        <v>2.792773759684887</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04674642881308923</v>
+      </c>
+      <c r="W61">
+        <v>0.2276369527994343</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2337321440654463</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2515241580274312</v>
+      </c>
+      <c r="C62">
+        <v>-5.481370841026326</v>
+      </c>
+      <c r="D62">
+        <v>33.28062915897367</v>
+      </c>
+      <c r="E62">
+        <v>43.412</v>
+      </c>
+      <c r="F62">
+        <v>45.732</v>
+      </c>
+      <c r="G62">
+        <v>6.97</v>
+      </c>
+      <c r="H62">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.93</v>
+      </c>
+      <c r="K62">
+        <v>1.42</v>
+      </c>
+      <c r="L62">
+        <v>2.51</v>
+      </c>
+      <c r="M62">
+        <v>10.9208016</v>
+      </c>
+      <c r="N62">
+        <v>-8.410801600000001</v>
+      </c>
+      <c r="O62">
+        <v>-1.68216032</v>
+      </c>
+      <c r="P62">
+        <v>-6.728641280000002</v>
+      </c>
+      <c r="Q62">
+        <v>-5.308641280000002</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2870758896894123</v>
+      </c>
+      <c r="T62">
+        <v>2.862593103677009</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04596732166620442</v>
+      </c>
+      <c r="W62">
+        <v>0.2278230035861104</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2298366083310222</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2535241580274312</v>
+      </c>
+      <c r="C63">
+        <v>-6.553555795348259</v>
+      </c>
+      <c r="D63">
+        <v>32.97064420465174</v>
+      </c>
+      <c r="E63">
+        <v>44.1742</v>
+      </c>
+      <c r="F63">
+        <v>46.4942</v>
+      </c>
+      <c r="G63">
+        <v>6.97</v>
+      </c>
+      <c r="H63">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.93</v>
+      </c>
+      <c r="K63">
+        <v>1.42</v>
+      </c>
+      <c r="L63">
+        <v>2.51</v>
+      </c>
+      <c r="M63">
+        <v>11.10281496</v>
+      </c>
+      <c r="N63">
+        <v>-8.59281496</v>
+      </c>
+      <c r="O63">
+        <v>-1.718562992</v>
+      </c>
+      <c r="P63">
+        <v>-6.874251968</v>
+      </c>
+      <c r="Q63">
+        <v>-5.454251967999999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2934419381429871</v>
+      </c>
+      <c r="T63">
+        <v>2.935992926848215</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04521375901593877</v>
+      </c>
+      <c r="W63">
+        <v>0.2280029543469939</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2260687950796939</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2555241580274312</v>
+      </c>
+      <c r="C64">
+        <v>-7.620019468625308</v>
+      </c>
+      <c r="D64">
+        <v>32.66638053137469</v>
+      </c>
+      <c r="E64">
+        <v>44.9364</v>
+      </c>
+      <c r="F64">
+        <v>47.2564</v>
+      </c>
+      <c r="G64">
+        <v>6.97</v>
+      </c>
+      <c r="H64">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.93</v>
+      </c>
+      <c r="K64">
+        <v>1.42</v>
+      </c>
+      <c r="L64">
+        <v>2.51</v>
+      </c>
+      <c r="M64">
+        <v>11.28482832</v>
+      </c>
+      <c r="N64">
+        <v>-8.774828320000001</v>
+      </c>
+      <c r="O64">
+        <v>-1.754965664</v>
+      </c>
+      <c r="P64">
+        <v>-7.019862656000001</v>
+      </c>
+      <c r="Q64">
+        <v>-5.599862656000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3001430417783287</v>
+      </c>
+      <c r="T64">
+        <v>3.013255898607378</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.04448450483826234</v>
+      </c>
+      <c r="W64">
+        <v>0.228177100244623</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2224225241913117</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2575241580274312</v>
+      </c>
+      <c r="C65">
+        <v>-8.680918805963962</v>
+      </c>
+      <c r="D65">
+        <v>32.36768119403604</v>
+      </c>
+      <c r="E65">
+        <v>45.6986</v>
+      </c>
+      <c r="F65">
+        <v>48.0186</v>
+      </c>
+      <c r="G65">
+        <v>6.97</v>
+      </c>
+      <c r="H65">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.93</v>
+      </c>
+      <c r="K65">
+        <v>1.42</v>
+      </c>
+      <c r="L65">
+        <v>2.51</v>
+      </c>
+      <c r="M65">
+        <v>11.46684168</v>
+      </c>
+      <c r="N65">
+        <v>-8.95684168</v>
+      </c>
+      <c r="O65">
+        <v>-1.791368336</v>
+      </c>
+      <c r="P65">
+        <v>-7.165473344</v>
+      </c>
+      <c r="Q65">
+        <v>-5.745473344000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3072063672317971</v>
+      </c>
+      <c r="T65">
+        <v>3.094695247218389</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.04377840158686135</v>
+      </c>
+      <c r="W65">
+        <v>0.2283457177010575</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2188920079343067</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2595241580274312</v>
+      </c>
+      <c r="C66">
+        <v>-9.736405064099905</v>
+      </c>
+      <c r="D66">
+        <v>32.0743949359001</v>
+      </c>
+      <c r="E66">
+        <v>46.4608</v>
+      </c>
+      <c r="F66">
+        <v>48.7808</v>
+      </c>
+      <c r="G66">
+        <v>6.97</v>
+      </c>
+      <c r="H66">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.93</v>
+      </c>
+      <c r="K66">
+        <v>1.42</v>
+      </c>
+      <c r="L66">
+        <v>2.51</v>
+      </c>
+      <c r="M66">
+        <v>11.64885504</v>
+      </c>
+      <c r="N66">
+        <v>-9.138855040000001</v>
+      </c>
+      <c r="O66">
+        <v>-1.827771008</v>
+      </c>
+      <c r="P66">
+        <v>-7.311084032000001</v>
+      </c>
+      <c r="Q66">
+        <v>-5.891084032</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3146620996549025</v>
+      </c>
+      <c r="T66">
+        <v>3.180659004085566</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.04309436406206664</v>
+      </c>
+      <c r="W66">
+        <v>0.2285090658619785</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2154718203103332</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2615241580274312</v>
+      </c>
+      <c r="C67">
+        <v>-10.78662406679786</v>
+      </c>
+      <c r="D67">
+        <v>31.78637593320214</v>
+      </c>
+      <c r="E67">
+        <v>47.223</v>
+      </c>
+      <c r="F67">
+        <v>49.543</v>
+      </c>
+      <c r="G67">
+        <v>6.97</v>
+      </c>
+      <c r="H67">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.93</v>
+      </c>
+      <c r="K67">
+        <v>1.42</v>
+      </c>
+      <c r="L67">
+        <v>2.51</v>
+      </c>
+      <c r="M67">
+        <v>11.8308684</v>
+      </c>
+      <c r="N67">
+        <v>-9.3208684</v>
+      </c>
+      <c r="O67">
+        <v>-1.86417368</v>
+      </c>
+      <c r="P67">
+        <v>-7.456694720000001</v>
+      </c>
+      <c r="Q67">
+        <v>-6.03669472</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.322543873930757</v>
+      </c>
+      <c r="T67">
+        <v>3.271534975630868</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.04243137384572715</v>
+      </c>
+      <c r="W67">
+        <v>0.2286673879256404</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2121568692286359</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2635241580274312</v>
+      </c>
+      <c r="C68">
+        <v>-11.83171644661331</v>
+      </c>
+      <c r="D68">
+        <v>31.50348355338669</v>
+      </c>
+      <c r="E68">
+        <v>47.9852</v>
+      </c>
+      <c r="F68">
+        <v>50.3052</v>
+      </c>
+      <c r="G68">
+        <v>6.97</v>
+      </c>
+      <c r="H68">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.93</v>
+      </c>
+      <c r="K68">
+        <v>1.42</v>
+      </c>
+      <c r="L68">
+        <v>2.51</v>
+      </c>
+      <c r="M68">
+        <v>12.01288176</v>
+      </c>
+      <c r="N68">
+        <v>-9.502881760000001</v>
+      </c>
+      <c r="O68">
+        <v>-1.900576352</v>
+      </c>
+      <c r="P68">
+        <v>-7.602305408000001</v>
+      </c>
+      <c r="Q68">
+        <v>-6.182305408000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3308892819875439</v>
+      </c>
+      <c r="T68">
+        <v>3.367756592561188</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.04178847424200401</v>
+      </c>
+      <c r="W68">
+        <v>0.2288209123510095</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2089423712100201</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2655241580274312</v>
+      </c>
+      <c r="C69">
+        <v>-12.87181787385843</v>
+      </c>
+      <c r="D69">
+        <v>31.22558212614156</v>
+      </c>
+      <c r="E69">
+        <v>48.7474</v>
+      </c>
+      <c r="F69">
+        <v>51.0674</v>
+      </c>
+      <c r="G69">
+        <v>6.97</v>
+      </c>
+      <c r="H69">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.93</v>
+      </c>
+      <c r="K69">
+        <v>1.42</v>
+      </c>
+      <c r="L69">
+        <v>2.51</v>
+      </c>
+      <c r="M69">
+        <v>12.19489512</v>
+      </c>
+      <c r="N69">
+        <v>-9.68489512</v>
+      </c>
+      <c r="O69">
+        <v>-1.936979024</v>
+      </c>
+      <c r="P69">
+        <v>-7.747916096000001</v>
+      </c>
+      <c r="Q69">
+        <v>-6.327916096000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3397404723508029</v>
+      </c>
+      <c r="T69">
+        <v>3.4698098226388</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.04116476567122784</v>
+      </c>
+      <c r="W69">
+        <v>0.2289698539577108</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2058238283561392</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2675241580274312</v>
+      </c>
+      <c r="C70">
+        <v>-13.90705927355525</v>
+      </c>
+      <c r="D70">
+        <v>30.95254072644476</v>
+      </c>
+      <c r="E70">
+        <v>49.50960000000001</v>
+      </c>
+      <c r="F70">
+        <v>51.82960000000001</v>
+      </c>
+      <c r="G70">
+        <v>6.97</v>
+      </c>
+      <c r="H70">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.93</v>
+      </c>
+      <c r="K70">
+        <v>1.42</v>
+      </c>
+      <c r="L70">
+        <v>2.51</v>
+      </c>
+      <c r="M70">
+        <v>12.37690848</v>
+      </c>
+      <c r="N70">
+        <v>-9.866908480000003</v>
+      </c>
+      <c r="O70">
+        <v>-1.973381696</v>
+      </c>
+      <c r="P70">
+        <v>-7.893526784000002</v>
+      </c>
+      <c r="Q70">
+        <v>-6.473526784000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3491448621117655</v>
+      </c>
+      <c r="T70">
+        <v>3.578241379596262</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.04055940147018036</v>
+      </c>
+      <c r="W70">
+        <v>0.229114414928921</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2027970073509018</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2695241580274312</v>
+      </c>
+      <c r="C71">
+        <v>-14.93756703110498</v>
+      </c>
+      <c r="D71">
+        <v>30.68423296889503</v>
+      </c>
+      <c r="E71">
+        <v>50.27180000000001</v>
+      </c>
+      <c r="F71">
+        <v>52.59180000000001</v>
+      </c>
+      <c r="G71">
+        <v>6.97</v>
+      </c>
+      <c r="H71">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.93</v>
+      </c>
+      <c r="K71">
+        <v>1.42</v>
+      </c>
+      <c r="L71">
+        <v>2.51</v>
+      </c>
+      <c r="M71">
+        <v>12.55892184</v>
+      </c>
+      <c r="N71">
+        <v>-10.04892184</v>
+      </c>
+      <c r="O71">
+        <v>-2.009784368</v>
+      </c>
+      <c r="P71">
+        <v>-8.039137472000002</v>
+      </c>
+      <c r="Q71">
+        <v>-6.619137472000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.359155986696016</v>
+      </c>
+      <c r="T71">
+        <v>3.693668520873561</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03997158405756905</v>
+      </c>
+      <c r="W71">
+        <v>0.2292547857270525</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1998579202878453</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2715241580274312</v>
+      </c>
+      <c r="C72">
+        <v>-15.96346318735257</v>
+      </c>
+      <c r="D72">
+        <v>30.42053681264744</v>
+      </c>
+      <c r="E72">
+        <v>51.03400000000001</v>
+      </c>
+      <c r="F72">
+        <v>53.35400000000001</v>
+      </c>
+      <c r="G72">
+        <v>6.97</v>
+      </c>
+      <c r="H72">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.93</v>
+      </c>
+      <c r="K72">
+        <v>1.42</v>
+      </c>
+      <c r="L72">
+        <v>2.51</v>
+      </c>
+      <c r="M72">
+        <v>12.7409352</v>
+      </c>
+      <c r="N72">
+        <v>-10.2309352</v>
+      </c>
+      <c r="O72">
+        <v>-2.04618704</v>
+      </c>
+      <c r="P72">
+        <v>-8.184748160000003</v>
+      </c>
+      <c r="Q72">
+        <v>-6.764748160000003</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3698345195858831</v>
+      </c>
+      <c r="T72">
+        <v>3.81679080490268</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0394005614281752</v>
+      </c>
+      <c r="W72">
+        <v>0.2293911459309518</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.197002807140876</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2735241580274312</v>
+      </c>
+      <c r="C73">
+        <v>-16.98486562367863</v>
+      </c>
+      <c r="D73">
+        <v>30.16133437632137</v>
+      </c>
+      <c r="E73">
+        <v>51.7962</v>
+      </c>
+      <c r="F73">
+        <v>54.1162</v>
+      </c>
+      <c r="G73">
+        <v>6.97</v>
+      </c>
+      <c r="H73">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.93</v>
+      </c>
+      <c r="K73">
+        <v>1.42</v>
+      </c>
+      <c r="L73">
+        <v>2.51</v>
+      </c>
+      <c r="M73">
+        <v>12.92294856</v>
+      </c>
+      <c r="N73">
+        <v>-10.41294856</v>
+      </c>
+      <c r="O73">
+        <v>-2.082589711999999</v>
+      </c>
+      <c r="P73">
+        <v>-8.330358848000001</v>
+      </c>
+      <c r="Q73">
+        <v>-6.910358848000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3812495030198791</v>
+      </c>
+      <c r="T73">
+        <v>3.948404280933806</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03884562394327134</v>
+      </c>
+      <c r="W73">
+        <v>0.2295236650023468</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1942281197163567</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2755241580274312</v>
+      </c>
+      <c r="C74">
+        <v>-18.0018882377088</v>
+      </c>
+      <c r="D74">
+        <v>29.90651176229119</v>
+      </c>
+      <c r="E74">
+        <v>52.5584</v>
+      </c>
+      <c r="F74">
+        <v>54.8784</v>
+      </c>
+      <c r="G74">
+        <v>6.97</v>
+      </c>
+      <c r="H74">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.93</v>
+      </c>
+      <c r="K74">
+        <v>1.42</v>
+      </c>
+      <c r="L74">
+        <v>2.51</v>
+      </c>
+      <c r="M74">
+        <v>13.10496192</v>
+      </c>
+      <c r="N74">
+        <v>-10.59496192</v>
+      </c>
+      <c r="O74">
+        <v>-2.118992384</v>
+      </c>
+      <c r="P74">
+        <v>-8.475969536000001</v>
+      </c>
+      <c r="Q74">
+        <v>-7.055969536000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3934798424134462</v>
+      </c>
+      <c r="T74">
+        <v>4.089418719538584</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03830610138850368</v>
+      </c>
+      <c r="W74">
+        <v>0.2296525029884253</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1915305069425184</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2775241580274311</v>
+      </c>
+      <c r="C75">
+        <v>-19.01464111019065</v>
+      </c>
+      <c r="D75">
+        <v>29.65595888980936</v>
+      </c>
+      <c r="E75">
+        <v>53.3206</v>
+      </c>
+      <c r="F75">
+        <v>55.6406</v>
+      </c>
+      <c r="G75">
+        <v>6.97</v>
+      </c>
+      <c r="H75">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.93</v>
+      </c>
+      <c r="K75">
+        <v>1.42</v>
+      </c>
+      <c r="L75">
+        <v>2.51</v>
+      </c>
+      <c r="M75">
+        <v>13.28697528</v>
+      </c>
+      <c r="N75">
+        <v>-10.77697528</v>
+      </c>
+      <c r="O75">
+        <v>-2.155395056</v>
+      </c>
+      <c r="P75">
+        <v>-8.621580224000001</v>
+      </c>
+      <c r="Q75">
+        <v>-7.201580224000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4066161328732034</v>
+      </c>
+      <c r="T75">
+        <v>4.240878672114087</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03778136027359267</v>
+      </c>
+      <c r="W75">
+        <v>0.2297778111666661</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1889068013679633</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2795241580274311</v>
+      </c>
+      <c r="C76">
+        <v>-20.0232306635518</v>
+      </c>
+      <c r="D76">
+        <v>29.4095693364482</v>
+      </c>
+      <c r="E76">
+        <v>54.0828</v>
+      </c>
+      <c r="F76">
+        <v>56.4028</v>
+      </c>
+      <c r="G76">
+        <v>6.97</v>
+      </c>
+      <c r="H76">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.93</v>
+      </c>
+      <c r="K76">
+        <v>1.42</v>
+      </c>
+      <c r="L76">
+        <v>2.51</v>
+      </c>
+      <c r="M76">
+        <v>13.46898864</v>
+      </c>
+      <c r="N76">
+        <v>-10.95898864</v>
+      </c>
+      <c r="O76">
+        <v>-2.191797728</v>
+      </c>
+      <c r="P76">
+        <v>-8.767190912000002</v>
+      </c>
+      <c r="Q76">
+        <v>-7.347190912000002</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4207629072144805</v>
+      </c>
+      <c r="T76">
+        <v>4.403989390272321</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03727080135097655</v>
+      </c>
+      <c r="W76">
+        <v>0.2298997326373868</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1863540067548828</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2815241580274311</v>
+      </c>
+      <c r="C77">
+        <v>-21.02775981261923</v>
+      </c>
+      <c r="D77">
+        <v>29.16724018738077</v>
+      </c>
+      <c r="E77">
+        <v>54.845</v>
+      </c>
+      <c r="F77">
+        <v>57.165</v>
+      </c>
+      <c r="G77">
+        <v>6.97</v>
+      </c>
+      <c r="H77">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.93</v>
+      </c>
+      <c r="K77">
+        <v>1.42</v>
+      </c>
+      <c r="L77">
+        <v>2.51</v>
+      </c>
+      <c r="M77">
+        <v>13.651002</v>
+      </c>
+      <c r="N77">
+        <v>-11.141002</v>
+      </c>
+      <c r="O77">
+        <v>-2.2282004</v>
+      </c>
+      <c r="P77">
+        <v>-8.912801600000002</v>
+      </c>
+      <c r="Q77">
+        <v>-7.492801600000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4360414235030597</v>
+      </c>
+      <c r="T77">
+        <v>4.580148965883215</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03677385733296353</v>
+      </c>
+      <c r="W77">
+        <v>0.2300184028688883</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1838692866648177</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2835241580274312</v>
+      </c>
+      <c r="C78">
+        <v>-22.02832810794798</v>
+      </c>
+      <c r="D78">
+        <v>28.92887189205202</v>
+      </c>
+      <c r="E78">
+        <v>55.6072</v>
+      </c>
+      <c r="F78">
+        <v>57.9272</v>
+      </c>
+      <c r="G78">
+        <v>6.97</v>
+      </c>
+      <c r="H78">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.93</v>
+      </c>
+      <c r="K78">
+        <v>1.42</v>
+      </c>
+      <c r="L78">
+        <v>2.51</v>
+      </c>
+      <c r="M78">
+        <v>13.83301536</v>
+      </c>
+      <c r="N78">
+        <v>-11.32301536</v>
+      </c>
+      <c r="O78">
+        <v>-2.264603072</v>
+      </c>
+      <c r="P78">
+        <v>-9.058412288000001</v>
+      </c>
+      <c r="Q78">
+        <v>-7.638412288000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.452593149482354</v>
+      </c>
+      <c r="T78">
+        <v>4.77098850612835</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03628999078910874</v>
+      </c>
+      <c r="W78">
+        <v>0.2301339501995608</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1814499539455438</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2855241580274311</v>
+      </c>
+      <c r="C79">
+        <v>-23.02503187217877</v>
+      </c>
+      <c r="D79">
+        <v>28.69436812782124</v>
+      </c>
+      <c r="E79">
+        <v>56.3694</v>
+      </c>
+      <c r="F79">
+        <v>58.6894</v>
+      </c>
+      <c r="G79">
+        <v>6.97</v>
+      </c>
+      <c r="H79">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.93</v>
+      </c>
+      <c r="K79">
+        <v>1.42</v>
+      </c>
+      <c r="L79">
+        <v>2.51</v>
+      </c>
+      <c r="M79">
+        <v>14.01502872</v>
+      </c>
+      <c r="N79">
+        <v>-11.50502872</v>
+      </c>
+      <c r="O79">
+        <v>-2.301005743999999</v>
+      </c>
+      <c r="P79">
+        <v>-9.204022976000001</v>
+      </c>
+      <c r="Q79">
+        <v>-7.784022976000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4705841559815867</v>
+      </c>
+      <c r="T79">
+        <v>4.978422789003495</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03581869220743201</v>
+      </c>
+      <c r="W79">
+        <v>0.2302464963008652</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1790934610371601</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2875241580274312</v>
+      </c>
+      <c r="C80">
+        <v>-24.0179643298169</v>
+      </c>
+      <c r="D80">
+        <v>28.4636356701831</v>
+      </c>
+      <c r="E80">
+        <v>57.1316</v>
+      </c>
+      <c r="F80">
+        <v>59.4516</v>
+      </c>
+      <c r="G80">
+        <v>6.97</v>
+      </c>
+      <c r="H80">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.93</v>
+      </c>
+      <c r="K80">
+        <v>1.42</v>
+      </c>
+      <c r="L80">
+        <v>2.51</v>
+      </c>
+      <c r="M80">
+        <v>14.19704208</v>
+      </c>
+      <c r="N80">
+        <v>-11.68704208</v>
+      </c>
+      <c r="O80">
+        <v>-2.337408416</v>
+      </c>
+      <c r="P80">
+        <v>-9.349633664000002</v>
+      </c>
+      <c r="Q80">
+        <v>-7.929633664000002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4902107085262044</v>
+      </c>
+      <c r="T80">
+        <v>5.2047147339582</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03535947820477262</v>
+      </c>
+      <c r="W80">
+        <v>0.2303561566047003</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1767973910238632</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2895241580274311</v>
+      </c>
+      <c r="C81">
+        <v>-25.00721573079971</v>
+      </c>
+      <c r="D81">
+        <v>28.23658426920029</v>
+      </c>
+      <c r="E81">
+        <v>57.8938</v>
+      </c>
+      <c r="F81">
+        <v>60.2138</v>
+      </c>
+      <c r="G81">
+        <v>6.97</v>
+      </c>
+      <c r="H81">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.93</v>
+      </c>
+      <c r="K81">
+        <v>1.42</v>
+      </c>
+      <c r="L81">
+        <v>2.51</v>
+      </c>
+      <c r="M81">
+        <v>14.37905544</v>
+      </c>
+      <c r="N81">
+        <v>-11.86905544</v>
+      </c>
+      <c r="O81">
+        <v>-2.373811088</v>
+      </c>
+      <c r="P81">
+        <v>-9.495244352</v>
+      </c>
+      <c r="Q81">
+        <v>-8.075244352</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5117064565512617</v>
+      </c>
+      <c r="T81">
+        <v>5.452558292718114</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03491188987306665</v>
+      </c>
+      <c r="W81">
+        <v>0.2304630406983117</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1745594493653333</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2915241580274312</v>
+      </c>
+      <c r="C82">
+        <v>-25.99287346819683</v>
+      </c>
+      <c r="D82">
+        <v>28.01312653180317</v>
+      </c>
+      <c r="E82">
+        <v>58.656</v>
+      </c>
+      <c r="F82">
+        <v>60.976</v>
+      </c>
+      <c r="G82">
+        <v>6.97</v>
+      </c>
+      <c r="H82">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.93</v>
+      </c>
+      <c r="K82">
+        <v>1.42</v>
+      </c>
+      <c r="L82">
+        <v>2.51</v>
+      </c>
+      <c r="M82">
+        <v>14.5610688</v>
+      </c>
+      <c r="N82">
+        <v>-12.0510688</v>
+      </c>
+      <c r="O82">
+        <v>-2.41021376</v>
+      </c>
+      <c r="P82">
+        <v>-9.640855040000002</v>
+      </c>
+      <c r="Q82">
+        <v>-8.220855040000002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5353517793788247</v>
+      </c>
+      <c r="T82">
+        <v>5.72518620735402</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03447549124965331</v>
+      </c>
+      <c r="W82">
+        <v>0.2305672526895828</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1723774562482666</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2935241580274311</v>
+      </c>
+      <c r="C83">
+        <v>-26.97502219036544</v>
+      </c>
+      <c r="D83">
+        <v>27.79317780963457</v>
+      </c>
+      <c r="E83">
+        <v>59.41820000000001</v>
+      </c>
+      <c r="F83">
+        <v>61.73820000000001</v>
+      </c>
+      <c r="G83">
+        <v>6.97</v>
+      </c>
+      <c r="H83">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.93</v>
+      </c>
+      <c r="K83">
+        <v>1.42</v>
+      </c>
+      <c r="L83">
+        <v>2.51</v>
+      </c>
+      <c r="M83">
+        <v>14.74308216</v>
+      </c>
+      <c r="N83">
+        <v>-12.23308216</v>
+      </c>
+      <c r="O83">
+        <v>-2.446616432</v>
+      </c>
+      <c r="P83">
+        <v>-9.786465728000003</v>
+      </c>
+      <c r="Q83">
+        <v>-8.366465728000003</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5614860835566577</v>
+      </c>
+      <c r="T83">
+        <v>6.026511797214758</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03404986790089216</v>
+      </c>
+      <c r="W83">
+        <v>0.230668891545267</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1702493395044609</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2955241580274311</v>
+      </c>
+      <c r="C84">
+        <v>-27.9537439078632</v>
+      </c>
+      <c r="D84">
+        <v>27.5766560921368</v>
+      </c>
+      <c r="E84">
+        <v>60.18040000000001</v>
+      </c>
+      <c r="F84">
+        <v>62.50040000000001</v>
+      </c>
+      <c r="G84">
+        <v>6.97</v>
+      </c>
+      <c r="H84">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.93</v>
+      </c>
+      <c r="K84">
+        <v>1.42</v>
+      </c>
+      <c r="L84">
+        <v>2.51</v>
+      </c>
+      <c r="M84">
+        <v>14.92509552</v>
+      </c>
+      <c r="N84">
+        <v>-12.41509552</v>
+      </c>
+      <c r="O84">
+        <v>-2.483019104</v>
+      </c>
+      <c r="P84">
+        <v>-9.932076416000003</v>
+      </c>
+      <c r="Q84">
+        <v>-8.512076416000003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5905241993098054</v>
+      </c>
+      <c r="T84">
+        <v>6.361318008171134</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03363462560941786</v>
+      </c>
+      <c r="W84">
+        <v>0.230768051404471</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1681731280470893</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2975241580274312</v>
+      </c>
+      <c r="C85">
+        <v>-28.92911809540245</v>
+      </c>
+      <c r="D85">
+        <v>27.36348190459756</v>
+      </c>
+      <c r="E85">
+        <v>60.94260000000001</v>
+      </c>
+      <c r="F85">
+        <v>63.26260000000001</v>
+      </c>
+      <c r="G85">
+        <v>6.97</v>
+      </c>
+      <c r="H85">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.93</v>
+      </c>
+      <c r="K85">
+        <v>1.42</v>
+      </c>
+      <c r="L85">
+        <v>2.51</v>
+      </c>
+      <c r="M85">
+        <v>15.10710888</v>
+      </c>
+      <c r="N85">
+        <v>-12.59710888</v>
+      </c>
+      <c r="O85">
+        <v>-2.519421776</v>
+      </c>
+      <c r="P85">
+        <v>-10.077687104</v>
+      </c>
+      <c r="Q85">
+        <v>-8.657687104000003</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.622978563975088</v>
+      </c>
+      <c r="T85">
+        <v>6.735513185122377</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03322938915629235</v>
+      </c>
+      <c r="W85">
+        <v>0.2308648218694774</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1661469457814617</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2995241580274312</v>
+      </c>
+      <c r="C86">
+        <v>-29.90122178911171</v>
+      </c>
+      <c r="D86">
+        <v>27.15357821088829</v>
+      </c>
+      <c r="E86">
+        <v>61.7048</v>
+      </c>
+      <c r="F86">
+        <v>64.0248</v>
+      </c>
+      <c r="G86">
+        <v>6.97</v>
+      </c>
+      <c r="H86">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.93</v>
+      </c>
+      <c r="K86">
+        <v>1.42</v>
+      </c>
+      <c r="L86">
+        <v>2.51</v>
+      </c>
+      <c r="M86">
+        <v>15.28912224</v>
+      </c>
+      <c r="N86">
+        <v>-12.77912224</v>
+      </c>
+      <c r="O86">
+        <v>-2.555824448</v>
+      </c>
+      <c r="P86">
+        <v>-10.223297792</v>
+      </c>
+      <c r="Q86">
+        <v>-8.803297792000002</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6594897242235307</v>
+      </c>
+      <c r="T86">
+        <v>7.156482759192523</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03283380119014601</v>
+      </c>
+      <c r="W86">
+        <v>0.2309592882757932</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.16416900595073</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3015241580274312</v>
+      </c>
+      <c r="C87">
+        <v>-30.87012967935492</v>
+      </c>
+      <c r="D87">
+        <v>26.94687032064507</v>
+      </c>
+      <c r="E87">
+        <v>62.46699999999999</v>
+      </c>
+      <c r="F87">
+        <v>64.78699999999999</v>
+      </c>
+      <c r="G87">
+        <v>6.97</v>
+      </c>
+      <c r="H87">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.93</v>
+      </c>
+      <c r="K87">
+        <v>1.42</v>
+      </c>
+      <c r="L87">
+        <v>2.51</v>
+      </c>
+      <c r="M87">
+        <v>15.4711356</v>
+      </c>
+      <c r="N87">
+        <v>-12.9611356</v>
+      </c>
+      <c r="O87">
+        <v>-2.592227119999999</v>
+      </c>
+      <c r="P87">
+        <v>-10.36890848</v>
+      </c>
+      <c r="Q87">
+        <v>-8.94890848</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.7008690391717662</v>
+      </c>
+      <c r="T87">
+        <v>7.633581609805358</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0324475211761443</v>
+      </c>
+      <c r="W87">
+        <v>0.2310515319431367</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1622376058807216</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3035241580274312</v>
+      </c>
+      <c r="C88">
+        <v>-31.83591419934312</v>
+      </c>
+      <c r="D88">
+        <v>26.74328580065688</v>
+      </c>
+      <c r="E88">
+        <v>63.2292</v>
+      </c>
+      <c r="F88">
+        <v>65.5492</v>
+      </c>
+      <c r="G88">
+        <v>6.97</v>
+      </c>
+      <c r="H88">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.93</v>
+      </c>
+      <c r="K88">
+        <v>1.42</v>
+      </c>
+      <c r="L88">
+        <v>2.51</v>
+      </c>
+      <c r="M88">
+        <v>15.65314896</v>
+      </c>
+      <c r="N88">
+        <v>-13.14314896</v>
+      </c>
+      <c r="O88">
+        <v>-2.628629791999999</v>
+      </c>
+      <c r="P88">
+        <v>-10.514519168</v>
+      </c>
+      <c r="Q88">
+        <v>-9.094519168000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7481596848268925</v>
+      </c>
+      <c r="T88">
+        <v>8.178837439077171</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03207022441828215</v>
+      </c>
+      <c r="W88">
+        <v>0.2311416304089143</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1603511220914108</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3055241580274312</v>
+      </c>
+      <c r="C89">
+        <v>-32.7986456097593</v>
+      </c>
+      <c r="D89">
+        <v>26.54275439024069</v>
+      </c>
+      <c r="E89">
+        <v>63.99139999999999</v>
+      </c>
+      <c r="F89">
+        <v>66.31139999999999</v>
+      </c>
+      <c r="G89">
+        <v>6.97</v>
+      </c>
+      <c r="H89">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.93</v>
+      </c>
+      <c r="K89">
+        <v>1.42</v>
+      </c>
+      <c r="L89">
+        <v>2.51</v>
+      </c>
+      <c r="M89">
+        <v>15.83516232</v>
+      </c>
+      <c r="N89">
+        <v>-13.32516232</v>
+      </c>
+      <c r="O89">
+        <v>-2.665032463999999</v>
+      </c>
+      <c r="P89">
+        <v>-10.660129856</v>
+      </c>
+      <c r="Q89">
+        <v>-9.240129855999999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8027258144289608</v>
+      </c>
+      <c r="T89">
+        <v>8.807978780544643</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03170160114910649</v>
+      </c>
+      <c r="W89">
+        <v>0.2312296576455934</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1585080057455325</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3075241580274312</v>
+      </c>
+      <c r="C90">
+        <v>-33.75839207960466</v>
+      </c>
+      <c r="D90">
+        <v>26.34520792039534</v>
+      </c>
+      <c r="E90">
+        <v>64.75360000000001</v>
+      </c>
+      <c r="F90">
+        <v>67.0736</v>
+      </c>
+      <c r="G90">
+        <v>6.97</v>
+      </c>
+      <c r="H90">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.93</v>
+      </c>
+      <c r="K90">
+        <v>1.42</v>
+      </c>
+      <c r="L90">
+        <v>2.51</v>
+      </c>
+      <c r="M90">
+        <v>16.01717568</v>
+      </c>
+      <c r="N90">
+        <v>-13.50717568</v>
+      </c>
+      <c r="O90">
+        <v>-2.701435136</v>
+      </c>
+      <c r="P90">
+        <v>-10.805740544</v>
+      </c>
+      <c r="Q90">
+        <v>-9.385740544000003</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.866386298964708</v>
+      </c>
+      <c r="T90">
+        <v>9.5419770122567</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03134135568150301</v>
+      </c>
+      <c r="W90">
+        <v>0.2313156842632571</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1567067784075151</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3095241580274312</v>
+      </c>
+      <c r="C91">
+        <v>-34.71521976346083</v>
+      </c>
+      <c r="D91">
+        <v>26.15058023653918</v>
+      </c>
+      <c r="E91">
+        <v>65.51580000000001</v>
+      </c>
+      <c r="F91">
+        <v>67.83580000000001</v>
+      </c>
+      <c r="G91">
+        <v>6.97</v>
+      </c>
+      <c r="H91">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.93</v>
+      </c>
+      <c r="K91">
+        <v>1.42</v>
+      </c>
+      <c r="L91">
+        <v>2.51</v>
+      </c>
+      <c r="M91">
+        <v>16.19918904</v>
+      </c>
+      <c r="N91">
+        <v>-13.68918904</v>
+      </c>
+      <c r="O91">
+        <v>-2.737837808</v>
+      </c>
+      <c r="P91">
+        <v>-10.951351232</v>
+      </c>
+      <c r="Q91">
+        <v>-9.531351232000004</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.9416214170524086</v>
+      </c>
+      <c r="T91">
+        <v>10.4094294679164</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03098920561766589</v>
+      </c>
+      <c r="W91">
+        <v>0.2313997776985014</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1549460280883295</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3115241580274312</v>
+      </c>
+      <c r="C92">
+        <v>-35.66919287535294</v>
+      </c>
+      <c r="D92">
+        <v>25.95880712464706</v>
+      </c>
+      <c r="E92">
+        <v>66.27800000000001</v>
+      </c>
+      <c r="F92">
+        <v>68.598</v>
+      </c>
+      <c r="G92">
+        <v>6.97</v>
+      </c>
+      <c r="H92">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.93</v>
+      </c>
+      <c r="K92">
+        <v>1.42</v>
+      </c>
+      <c r="L92">
+        <v>2.51</v>
+      </c>
+      <c r="M92">
+        <v>16.3812024</v>
+      </c>
+      <c r="N92">
+        <v>-13.8712024</v>
+      </c>
+      <c r="O92">
+        <v>-2.774240479999999</v>
+      </c>
+      <c r="P92">
+        <v>-11.09696192</v>
+      </c>
+      <c r="Q92">
+        <v>-9.67696192</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.031903558757649</v>
+      </c>
+      <c r="T92">
+        <v>11.45037241470804</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03064488111080295</v>
+      </c>
+      <c r="W92">
+        <v>0.2314820023907403</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1532244055540147</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3135241580274312</v>
+      </c>
+      <c r="C93">
+        <v>-36.62037375938613</v>
+      </c>
+      <c r="D93">
+        <v>25.76982624061388</v>
+      </c>
+      <c r="E93">
+        <v>67.04020000000001</v>
+      </c>
+      <c r="F93">
+        <v>69.36020000000001</v>
+      </c>
+      <c r="G93">
+        <v>6.97</v>
+      </c>
+      <c r="H93">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.93</v>
+      </c>
+      <c r="K93">
+        <v>1.42</v>
+      </c>
+      <c r="L93">
+        <v>2.51</v>
+      </c>
+      <c r="M93">
+        <v>16.56321576</v>
+      </c>
+      <c r="N93">
+        <v>-14.05321576</v>
+      </c>
+      <c r="O93">
+        <v>-2.810643152</v>
+      </c>
+      <c r="P93">
+        <v>-11.242572608</v>
+      </c>
+      <c r="Q93">
+        <v>-9.822572608000003</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.142248398619611</v>
+      </c>
+      <c r="T93">
+        <v>12.72263601634227</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03030812417551939</v>
+      </c>
+      <c r="W93">
+        <v>0.231562419946886</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.151540620877597</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3155241580274312</v>
+      </c>
+      <c r="C94">
+        <v>-37.56882295731888</v>
+      </c>
+      <c r="D94">
+        <v>25.58357704268112</v>
+      </c>
+      <c r="E94">
+        <v>67.80240000000001</v>
+      </c>
+      <c r="F94">
+        <v>70.1224</v>
+      </c>
+      <c r="G94">
+        <v>6.97</v>
+      </c>
+      <c r="H94">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.93</v>
+      </c>
+      <c r="K94">
+        <v>1.42</v>
+      </c>
+      <c r="L94">
+        <v>2.51</v>
+      </c>
+      <c r="M94">
+        <v>16.74522912</v>
+      </c>
+      <c r="N94">
+        <v>-14.23522912</v>
+      </c>
+      <c r="O94">
+        <v>-2.847045824</v>
+      </c>
+      <c r="P94">
+        <v>-11.388183296</v>
+      </c>
+      <c r="Q94">
+        <v>-9.968183296000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.280179448447062</v>
+      </c>
+      <c r="T94">
+        <v>14.31296551838506</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02997868804317679</v>
+      </c>
+      <c r="W94">
+        <v>0.2316410892952894</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.149893440215884</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3175241580274312</v>
+      </c>
+      <c r="C95">
+        <v>-38.51459927322735</v>
+      </c>
+      <c r="D95">
+        <v>25.40000072677266</v>
+      </c>
+      <c r="E95">
+        <v>68.56460000000001</v>
+      </c>
+      <c r="F95">
+        <v>70.88460000000001</v>
+      </c>
+      <c r="G95">
+        <v>6.97</v>
+      </c>
+      <c r="H95">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.93</v>
+      </c>
+      <c r="K95">
+        <v>1.42</v>
+      </c>
+      <c r="L95">
+        <v>2.51</v>
+      </c>
+      <c r="M95">
+        <v>16.92724248</v>
+      </c>
+      <c r="N95">
+        <v>-14.41724248</v>
+      </c>
+      <c r="O95">
+        <v>-2.883448496</v>
+      </c>
+      <c r="P95">
+        <v>-11.533793984</v>
+      </c>
+      <c r="Q95">
+        <v>-10.113793984</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.457519369653786</v>
+      </c>
+      <c r="T95">
+        <v>16.35767487815435</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02965633655884155</v>
+      </c>
+      <c r="W95">
+        <v>0.2317180668297486</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1482816827942078</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3195241580274312</v>
+      </c>
+      <c r="C96">
+        <v>-39.45775983540518</v>
+      </c>
+      <c r="D96">
+        <v>25.21904016459481</v>
+      </c>
+      <c r="E96">
+        <v>69.32680000000001</v>
+      </c>
+      <c r="F96">
+        <v>71.6468</v>
+      </c>
+      <c r="G96">
+        <v>6.97</v>
+      </c>
+      <c r="H96">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.93</v>
+      </c>
+      <c r="K96">
+        <v>1.42</v>
+      </c>
+      <c r="L96">
+        <v>2.51</v>
+      </c>
+      <c r="M96">
+        <v>17.10925584</v>
+      </c>
+      <c r="N96">
+        <v>-14.59925584</v>
+      </c>
+      <c r="O96">
+        <v>-2.919851167999999</v>
+      </c>
+      <c r="P96">
+        <v>-11.679404672</v>
+      </c>
+      <c r="Q96">
+        <v>-10.259404672</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.693972597929417</v>
+      </c>
+      <c r="T96">
+        <v>19.08395402451341</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02934084361672622</v>
+      </c>
+      <c r="W96">
+        <v>0.2317934065443258</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1467042180836311</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3215241580274312</v>
+      </c>
+      <c r="C97">
+        <v>-40.39836015563639</v>
+      </c>
+      <c r="D97">
+        <v>25.04063984436362</v>
+      </c>
+      <c r="E97">
+        <v>70.08900000000001</v>
+      </c>
+      <c r="F97">
+        <v>72.40900000000001</v>
+      </c>
+      <c r="G97">
+        <v>6.97</v>
+      </c>
+      <c r="H97">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.93</v>
+      </c>
+      <c r="K97">
+        <v>1.42</v>
+      </c>
+      <c r="L97">
+        <v>2.51</v>
+      </c>
+      <c r="M97">
+        <v>17.2912692</v>
+      </c>
+      <c r="N97">
+        <v>-14.7812692</v>
+      </c>
+      <c r="O97">
+        <v>-2.95625384</v>
+      </c>
+      <c r="P97">
+        <v>-11.82501536</v>
+      </c>
+      <c r="Q97">
+        <v>-10.40501536</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.025007117515301</v>
+      </c>
+      <c r="T97">
+        <v>22.90074482941611</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02903199263128699</v>
+      </c>
+      <c r="W97">
+        <v>0.2318671601596487</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.145159963156435</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3235241580274312</v>
+      </c>
+      <c r="C98">
+        <v>-41.33645418596978</v>
+      </c>
+      <c r="D98">
+        <v>24.86474581403022</v>
+      </c>
+      <c r="E98">
+        <v>70.85120000000001</v>
+      </c>
+      <c r="F98">
+        <v>73.1712</v>
+      </c>
+      <c r="G98">
+        <v>6.97</v>
+      </c>
+      <c r="H98">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.93</v>
+      </c>
+      <c r="K98">
+        <v>1.42</v>
+      </c>
+      <c r="L98">
+        <v>2.51</v>
+      </c>
+      <c r="M98">
+        <v>17.47328256</v>
+      </c>
+      <c r="N98">
+        <v>-14.96328256</v>
+      </c>
+      <c r="O98">
+        <v>-2.992656511999999</v>
+      </c>
+      <c r="P98">
+        <v>-11.970626048</v>
+      </c>
+      <c r="Q98">
+        <v>-10.550626048</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.521558896894122</v>
+      </c>
+      <c r="T98">
+        <v>28.62593103677007</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02872957604137776</v>
+      </c>
+      <c r="W98">
+        <v>0.231939377241319</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1436478802068888</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3255241580274312</v>
+      </c>
+      <c r="C99">
+        <v>-42.27209437311753</v>
+      </c>
+      <c r="D99">
+        <v>24.69130562688247</v>
+      </c>
+      <c r="E99">
+        <v>71.6134</v>
+      </c>
+      <c r="F99">
+        <v>73.93339999999999</v>
+      </c>
+      <c r="G99">
+        <v>6.97</v>
+      </c>
+      <c r="H99">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.93</v>
+      </c>
+      <c r="K99">
+        <v>1.42</v>
+      </c>
+      <c r="L99">
+        <v>2.51</v>
+      </c>
+      <c r="M99">
+        <v>17.65529592</v>
+      </c>
+      <c r="N99">
+        <v>-15.14529592</v>
+      </c>
+      <c r="O99">
+        <v>-3.029059183999999</v>
+      </c>
+      <c r="P99">
+        <v>-12.116236736</v>
+      </c>
+      <c r="Q99">
+        <v>-10.696236736</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.349145195858829</v>
+      </c>
+      <c r="T99">
+        <v>38.16790804902676</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02843339484507489</v>
+      </c>
+      <c r="W99">
+        <v>0.2320101053109961</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1421669742253745</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3275241580274312</v>
+      </c>
+      <c r="C100">
+        <v>-43.20533171059267</v>
+      </c>
+      <c r="D100">
+        <v>24.52026828940732</v>
+      </c>
+      <c r="E100">
+        <v>72.37560000000001</v>
+      </c>
+      <c r="F100">
+        <v>74.6956</v>
+      </c>
+      <c r="G100">
+        <v>6.97</v>
+      </c>
+      <c r="H100">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.93</v>
+      </c>
+      <c r="K100">
+        <v>1.42</v>
+      </c>
+      <c r="L100">
+        <v>2.51</v>
+      </c>
+      <c r="M100">
+        <v>17.83730928</v>
+      </c>
+      <c r="N100">
+        <v>-15.32730928</v>
+      </c>
+      <c r="O100">
+        <v>-3.065461855999999</v>
+      </c>
+      <c r="P100">
+        <v>-12.261847424</v>
+      </c>
+      <c r="Q100">
+        <v>-10.841847424</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.004317793788243</v>
+      </c>
+      <c r="T100">
+        <v>57.25186207354014</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0281432581629823</v>
+      </c>
+      <c r="W100">
+        <v>0.2320793899506798</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1407162908149115</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3295241580274312</v>
+      </c>
+      <c r="C101">
+        <v>-44.13621578869459</v>
+      </c>
+      <c r="D101">
+        <v>24.3515842113054</v>
+      </c>
+      <c r="E101">
+        <v>73.1378</v>
+      </c>
+      <c r="F101">
+        <v>75.45779999999999</v>
+      </c>
+      <c r="G101">
+        <v>6.97</v>
+      </c>
+      <c r="H101">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.93</v>
+      </c>
+      <c r="K101">
+        <v>1.42</v>
+      </c>
+      <c r="L101">
+        <v>2.51</v>
+      </c>
+      <c r="M101">
+        <v>18.01932264</v>
+      </c>
+      <c r="N101">
+        <v>-15.50932264</v>
+      </c>
+      <c r="O101">
+        <v>-3.101864527999999</v>
+      </c>
+      <c r="P101">
+        <v>-12.407458112</v>
+      </c>
+      <c r="Q101">
+        <v>-10.987458112</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.969835587576485</v>
+      </c>
+      <c r="T101">
+        <v>114.5037241470803</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02785898282800267</v>
+      </c>
+      <c r="W101">
+        <v>0.232147274900673</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1392949141400134</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
